--- a/data/trending_integrated_20260922_11.xlsx
+++ b/data/trending_integrated_20260922_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>34946858840</v>
+        <v>34953556190</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -619,19 +619,19 @@
         <v>15130</v>
       </c>
       <c r="R2" t="n">
-        <v>26000</v>
+        <v>138000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국내 NPU 기반 휴머노이드 개발 착수 및 인텔과의 협력 강화.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 및 인텔 협력사 선정. 로봇 속도 초가속 등 잭팟 메가톤급 재료 분석.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="F3" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G3" t="n">
-        <v>264</v>
+        <v>293</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5275012214</v>
+        <v>5298409564</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>67900</v>
+        <v>66800</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+29.83%</t>
+          <t>'+27.72%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="F4" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G4" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>124026625000</v>
+        <v>131563840750</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -803,23 +803,23 @@
         <v>16300</v>
       </c>
       <c r="R4" t="n">
-        <v>-18000</v>
+        <v>-2000</v>
       </c>
       <c r="S4" t="n">
-        <v>36000</v>
+        <v>49000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>29.83% 급등하며 심텍 대비 높은 상승률 기록. 6만원 이상 매도 의견과 키 맞추기 기대감 공존. 마이크론 실적 발표 변수.</t>
+          <t>반도체 업황 개선 기대 속에서 주가 상승 모멘텀. 6만원 이상 매도 구간 및 이격 축소, 20일선 안착 여부 관찰.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['키 맞추기', '실적 발표', '반도체']</t>
+          <t>['반도체', '이격축소', '20일선']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>117100</v>
+        <v>115200</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+14.92%</t>
+          <t>'+13.05%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F5" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H5" t="n">
         <v>18.2</v>
@@ -886,7 +886,7 @@
         <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>252573495150</v>
+        <v>255961064550</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -895,10 +895,10 @@
         <v>26350</v>
       </c>
       <c r="R5" t="n">
-        <v>213000</v>
+        <v>234000</v>
       </c>
       <c r="S5" t="n">
-        <v>5000</v>
+        <v>14000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32250</v>
+        <v>32200</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.59%</t>
+          <t>'+8.42%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -952,7 +952,7 @@
         <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H6" t="n">
         <v>11.3</v>
@@ -978,7 +978,7 @@
         <v>11.92</v>
       </c>
       <c r="O6" t="n">
-        <v>214069559800</v>
+        <v>216809384225</v>
       </c>
       <c r="P6" t="n">
         <v>75900</v>
@@ -987,14 +987,14 @@
         <v>15000</v>
       </c>
       <c r="R6" t="n">
-        <v>351000</v>
+        <v>262000</v>
       </c>
       <c r="S6" t="n">
-        <v>6000</v>
+        <v>4000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>가온전선 대비 부진한 주가 흐름 속에서 20% 상승 및 단기 3만 5천원 가능성 언급. AI 전력 수요 폭증 관련 기대감 형성.</t>
+          <t>AI 전력 수요 증가로 인한 전력기기 주식 주목. 다만, 700원 저항선 돌파 여부와 외인/기관 매도세 관찰 필요.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI 전력', '전력기기', '추세']</t>
+          <t>['AI 전력수요', '거래량', '외인기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6240</v>
+        <v>6230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.48%</t>
+          <t>'+6.31%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-0.19</v>
       </c>
       <c r="E7" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F7" t="n">
         <v>48</v>
       </c>
       <c r="G7" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0.19</v>
       </c>
       <c r="O7" t="n">
-        <v>53532345575</v>
+        <v>54619221670</v>
       </c>
       <c r="P7" t="n">
         <v>13140</v>
@@ -1079,10 +1079,10 @@
         <v>3725</v>
       </c>
       <c r="R7" t="n">
-        <v>168000</v>
+        <v>48000</v>
       </c>
       <c r="S7" t="n">
-        <v>23000</v>
+        <v>27000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1130,16 +1130,16 @@
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F8" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H8" t="n">
-        <v>51.75</v>
+        <v>51.76</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>55472455475</v>
+        <v>57600187900</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1171,10 +1171,10 @@
         <v>21000</v>
       </c>
       <c r="R8" t="n">
-        <v>125000</v>
+        <v>324000</v>
       </c>
       <c r="S8" t="n">
-        <v>38000</v>
+        <v>118000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6650</v>
+        <v>6620</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+5.39%</t>
+          <t>'+4.91%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H9" t="n">
         <v>4.86</v>
@@ -1254,7 +1254,7 @@
         <v>4.95</v>
       </c>
       <c r="O9" t="n">
-        <v>47025368255</v>
+        <v>47363447495</v>
       </c>
       <c r="P9" t="n">
         <v>11760</v>
@@ -1263,7 +1263,7 @@
         <v>1620</v>
       </c>
       <c r="R9" t="n">
-        <v>54000</v>
+        <v>-92000</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14070</v>
+        <v>14080</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.91%</t>
+          <t>'+3.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="H10" t="n">
         <v>3.34</v>
@@ -1346,7 +1346,7 @@
         <v>3.68</v>
       </c>
       <c r="O10" t="n">
-        <v>81031164605</v>
+        <v>81663648575</v>
       </c>
       <c r="P10" t="n">
         <v>20300</v>
@@ -1355,10 +1355,10 @@
         <v>2885</v>
       </c>
       <c r="R10" t="n">
-        <v>236000</v>
+        <v>18000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1391,31 +1391,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>330500</v>
+        <v>18890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.77%</t>
+          <t>'+3.28%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.4</v>
+        <v>-0.27</v>
       </c>
       <c r="E11" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="F11" t="n">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>231</v>
+        <v>394</v>
       </c>
       <c r="H11" t="n">
-        <v>3.22</v>
+        <v>10.47</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>318500</v>
+        <v>18290</v>
       </c>
       <c r="K11" t="n">
-        <v>333000</v>
+        <v>18830</v>
       </c>
       <c r="L11" t="n">
-        <v>349500</v>
+        <v>19540</v>
       </c>
       <c r="M11" t="n">
-        <v>325000</v>
+        <v>18540</v>
       </c>
       <c r="N11" t="n">
-        <v>3.62</v>
+        <v>10.74</v>
       </c>
       <c r="O11" t="n">
-        <v>97510102500</v>
+        <v>83732676775</v>
       </c>
       <c r="P11" t="n">
-        <v>635000</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>52600</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>3000</v>
+        <v>-76000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>미국 증시 상승과 구리 가격 상승에 따른 52주 신고가 경신 기대.</t>
+          <t>공매도 관련 이슈 제기 및 연기금 매수세 유입. LNG, 원전 관련 수주 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['신고가', '구리 가격', '나스닥']</t>
+          <t>['공매도', '연기금', 'LNG', '원전']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1919000</v>
+        <v>327500</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.83%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>96</v>
       </c>
       <c r="F12" t="n">
-        <v>476</v>
+        <v>66</v>
       </c>
       <c r="G12" t="n">
-        <v>3361</v>
+        <v>246</v>
       </c>
       <c r="H12" t="n">
-        <v>50.17</v>
+        <v>3.22</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1868000</v>
+        <v>318500</v>
       </c>
       <c r="K12" t="n">
-        <v>1909000</v>
+        <v>333000</v>
       </c>
       <c r="L12" t="n">
-        <v>1935000</v>
+        <v>349500</v>
       </c>
       <c r="M12" t="n">
-        <v>1904000</v>
+        <v>325000</v>
       </c>
       <c r="N12" t="n">
-        <v>50.23</v>
+        <v>3.62</v>
       </c>
       <c r="O12" t="n">
-        <v>2118597505000</v>
+        <v>99462323000</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>635000</v>
       </c>
       <c r="Q12" t="n">
-        <v>333000</v>
+        <v>52600</v>
       </c>
       <c r="R12" t="n">
-        <v>85000</v>
+        <v>-8000</v>
       </c>
       <c r="S12" t="n">
-        <v>55000</v>
+        <v>1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>미국 반도체주 폭등 및 코스피 200 야간 선물 상승에 힘입어 200만원 돌파 기대감 고조. 27년 상반기 500만원 목표.</t>
+          <t>나스닥 폭등 및 구리 가격 상승세에 따른 신고가 돌파 기대. 40만원 목표가 제시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '추세']</t>
+          <t>['신고가', '구리', '나스닥']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -1579,24 +1579,24 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13300</v>
+        <v>13280</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.62%</t>
+          <t>'+2.47%</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F13" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G13" t="n">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -1622,7 +1622,7 @@
         <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>18542480680</v>
+        <v>18715899100</v>
       </c>
       <c r="P13" t="n">
         <v>19380</v>
@@ -1631,7 +1631,7 @@
         <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-40000</v>
+        <v>-41000</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1667,11 +1667,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18730</v>
+        <v>1913000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.27</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>93</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>53</v>
+        <v>478</v>
       </c>
       <c r="G14" t="n">
-        <v>366</v>
+        <v>3258</v>
       </c>
       <c r="H14" t="n">
-        <v>10.47</v>
+        <v>50.17</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>18290</v>
+        <v>1868000</v>
       </c>
       <c r="K14" t="n">
-        <v>18830</v>
+        <v>1909000</v>
       </c>
       <c r="L14" t="n">
-        <v>19540</v>
+        <v>1935000</v>
       </c>
       <c r="M14" t="n">
-        <v>18540</v>
+        <v>1904000</v>
       </c>
       <c r="N14" t="n">
-        <v>10.74</v>
+        <v>50.23</v>
       </c>
       <c r="O14" t="n">
-        <v>80168697635</v>
+        <v>2199583973000</v>
       </c>
       <c r="P14" t="n">
-        <v>40350</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>3320</v>
+        <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>5000</v>
+        <v>82000</v>
       </c>
       <c r="S14" t="n">
-        <v>15000</v>
+        <v>44000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>체코 원전 수주 관련 긍정적 전망. 수조원 규모 수주 가능성 언급과 함께 공매도 세력에 대한 비판 제기. 연기금 순매수 확인.</t>
+          <t>미국 반도체 주가 폭등에 따른 국내 증시 동반 상승 기대. AI 관련주 강세 및 200만 돌파 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['원전', '수주', '공매도']</t>
+          <t>['AI', '반도체', '나스닥']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>21</v>
+        <v>76</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1774,13 +1774,13 @@
         <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F15" t="n">
         <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H15" t="n">
         <v>75.5</v>
@@ -1806,7 +1806,7 @@
         <v>75.44</v>
       </c>
       <c r="O15" t="n">
-        <v>427550256250</v>
+        <v>438389026750</v>
       </c>
       <c r="P15" t="n">
         <v>243500</v>
@@ -1815,10 +1815,10 @@
         <v>64700</v>
       </c>
       <c r="R15" t="n">
-        <v>-376000</v>
+        <v>-691000</v>
       </c>
       <c r="S15" t="n">
-        <v>12000</v>
+        <v>13000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>279750</v>
+        <v>279500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.10%</t>
+          <t>'+2.01%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="G16" t="n">
-        <v>2548</v>
+        <v>2314</v>
       </c>
       <c r="H16" t="n">
         <v>46.56</v>
@@ -1898,7 +1898,7 @@
         <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1678381630500</v>
+        <v>1754647726500</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1907,14 +1907,14 @@
         <v>81100</v>
       </c>
       <c r="R16" t="n">
-        <v>26000</v>
+        <v>-116000</v>
       </c>
       <c r="S16" t="n">
-        <v>42000</v>
+        <v>128000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>3분기 영업이익 발표 기대감 속 29만원 돌파 및 30만원 안착 가능성 언급. AI 낙관론 및 배당금 기대감 존재.</t>
+          <t>AI 낙관론에 따른 주가 상승 기대감. 배당금 기준일(28일)까지 긍정적 흐름 전망.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['영업이익', 'AI', '배당금']</t>
+          <t>['AI 낙관론', '배당금', '주가전망']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,184 +1943,184 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10680</v>
+        <v>86400</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+1.29%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>52</v>
+        <v>241</v>
       </c>
       <c r="F17" t="n">
-        <v>37</v>
+        <v>154</v>
       </c>
       <c r="G17" t="n">
-        <v>138</v>
+        <v>902</v>
       </c>
       <c r="H17" t="n">
-        <v>9.609999999999999</v>
+        <v>23.05</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10550</v>
+        <v>85300</v>
       </c>
       <c r="K17" t="n">
-        <v>10730</v>
+        <v>87000</v>
       </c>
       <c r="L17" t="n">
-        <v>11160</v>
+        <v>87000</v>
       </c>
       <c r="M17" t="n">
-        <v>10300</v>
+        <v>85200</v>
       </c>
       <c r="N17" t="n">
-        <v>8.6</v>
+        <v>23.12</v>
       </c>
       <c r="O17" t="n">
-        <v>107132817170</v>
+        <v>83333387450</v>
       </c>
       <c r="P17" t="n">
-        <v>11640</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3735</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>-140000</v>
+        <v>-200000</v>
       </c>
       <c r="S17" t="n">
-        <v>8000</v>
+        <v>-4000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>미국 SMR 투자 확정 및 공급 계약 체결 소식. 가스터빈 관련 기대감.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['SMR', '공급계약', '가스터빈']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>86000</v>
+        <v>10600</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.82%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="E18" t="n">
-        <v>223</v>
+        <v>57</v>
       </c>
       <c r="F18" t="n">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="G18" t="n">
-        <v>813</v>
+        <v>137</v>
       </c>
       <c r="H18" t="n">
-        <v>23.05</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>85300</v>
+        <v>10550</v>
       </c>
       <c r="K18" t="n">
-        <v>87000</v>
+        <v>10730</v>
       </c>
       <c r="L18" t="n">
-        <v>87000</v>
+        <v>11160</v>
       </c>
       <c r="M18" t="n">
-        <v>85200</v>
+        <v>10300</v>
       </c>
       <c r="N18" t="n">
-        <v>23.12</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
-        <v>79386599550</v>
+        <v>108698910335</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>11640</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>3735</v>
       </c>
       <c r="R18" t="n">
-        <v>-160000</v>
+        <v>209000</v>
       </c>
       <c r="S18" t="n">
-        <v>-6000</v>
+        <v>-38000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SMR 및 차세대 KDDX 전기추진 시스템 공급 계약 체결로 인한 상승 기대감 형성. 대미투자 관련 긍정적 뉴스 확인.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SMR', '공급 계약', '대미투자']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17770</v>
+        <v>17690</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.28%</t>
+          <t>'-0.17%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-1.68</v>
       </c>
       <c r="E19" t="n">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G19" t="n">
-        <v>592</v>
+        <v>609</v>
       </c>
       <c r="H19" t="n">
         <v>6.22</v>
@@ -2174,7 +2174,7 @@
         <v>7.9</v>
       </c>
       <c r="O19" t="n">
-        <v>120462496375</v>
+        <v>123761627340</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2183,10 +2183,10 @@
         <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-359000</v>
+        <v>-545000</v>
       </c>
       <c r="S19" t="n">
-        <v>5000</v>
+        <v>7000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8470</v>
+        <v>8500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.59%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F20" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="H20" t="n">
         <v>26.58</v>
@@ -2266,7 +2266,7 @@
         <v>26.57</v>
       </c>
       <c r="O20" t="n">
-        <v>13381808085</v>
+        <v>13676793515</v>
       </c>
       <c r="P20" t="n">
         <v>17950</v>
@@ -2275,14 +2275,14 @@
         <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>-212000</v>
+        <v>-418000</v>
       </c>
       <c r="S20" t="n">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>적자 회사 및 무능한 경영진 비판 속 8460원 부근 매수 의견. 외인 풀매도 및 개잡주 평가 존재.</t>
+          <t>회사의 재무 실적 부진 및 장기적인 비전 부재에 대한 부정적 의견. 외국인 매도세 관찰.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['적자', '외인 매도', '재무 실적']</t>
+          <t>['적자', '외인매도', '비전']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2315,24 +2315,24 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21150</v>
+        <v>21200</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.40%</t>
         </is>
       </c>
       <c r="D21" t="n">
         <v>-0.05</v>
       </c>
       <c r="E21" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="H21" t="n">
         <v>1.2</v>
@@ -2358,7 +2358,7 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>41227974150</v>
+        <v>41584057550</v>
       </c>
       <c r="P21" t="n">
         <v>22900</v>
@@ -2367,7 +2367,7 @@
         <v>9900</v>
       </c>
       <c r="R21" t="n">
-        <v>89000</v>
+        <v>47000</v>
       </c>
       <c r="S21" t="n">
         <v>-3000</v>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24050</v>
+        <v>24300</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-4.75%</t>
+          <t>'-3.76%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1.41</v>
       </c>
       <c r="E22" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F22" t="n">
         <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="H22" t="n">
         <v>1.76</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>89806145150</v>
+        <v>90990762325</v>
       </c>
       <c r="P22" t="n">
         <v>39350</v>
@@ -2459,7 +2459,7 @@
         <v>8200</v>
       </c>
       <c r="R22" t="n">
-        <v>-10000</v>
+        <v>20000</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2495,70 +2495,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>10510</v>
+        <v>3850</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-4.97%</t>
+          <t>'-5.06%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="F23" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G23" t="n">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="H23" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K23" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L23" t="n">
-        <v>10815</v>
+        <v>4080</v>
       </c>
       <c r="M23" t="n">
-        <v>10060</v>
+        <v>3825</v>
       </c>
       <c r="N23" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>31774751555</v>
+        <v>8799102305</v>
       </c>
       <c r="P23" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q23" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R23" t="n">
-        <v>3000</v>
+        <v>51000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 속에서 11000원 돌파 기대와 함께 차트 붕괴 및 급락 우려 공존. 종가 양전 시도.</t>
+          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['투자경고', '돌파', '차트']</t>
+          <t>['비트코인', '차트분석', '신용물량']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,77 +2580,77 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>017900</t>
+          <t>201490</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>광전자</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3850</v>
+        <v>10390</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.06%</t>
+          <t>'-6.06%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>0.63</v>
+        <v>-0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="F24" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>225</v>
+        <v>173</v>
       </c>
       <c r="H24" t="n">
-        <v>0.96</v>
+        <v>17.89</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>4055</v>
+        <v>11060</v>
       </c>
       <c r="K24" t="n">
-        <v>4080</v>
+        <v>10570</v>
       </c>
       <c r="L24" t="n">
-        <v>4080</v>
+        <v>10815</v>
       </c>
       <c r="M24" t="n">
-        <v>3845</v>
+        <v>10060</v>
       </c>
       <c r="N24" t="n">
-        <v>0.33</v>
+        <v>18.29</v>
       </c>
       <c r="O24" t="n">
-        <v>8380538061</v>
+        <v>32645106375</v>
       </c>
       <c r="P24" t="n">
-        <v>6480</v>
+        <v>22450</v>
       </c>
       <c r="Q24" t="n">
-        <v>1738</v>
+        <v>1760</v>
       </c>
       <c r="R24" t="n">
-        <v>-44000</v>
+        <v>-11000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
+          <t>투자경고 종목 지정 속에서 11000원 돌파 기대와 함께 차트 붕괴 및 급락 우려 공존. 종가 양전 시도.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,11 +2659,11 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>['비트코인', '차트분석', '신용물량']</t>
+          <t>['투자경고', '돌파', '차트']</t>
         </is>
       </c>
       <c r="X24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
@@ -2672,7 +2672,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>017900</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20260922_11.xlsx
+++ b/data/trending_integrated_20260922_11.xlsx
@@ -578,13 +578,13 @@
         <v>0.04</v>
       </c>
       <c r="E2" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H2" t="n">
         <v>0.6899999999999999</v>
@@ -610,7 +610,7 @@
         <v>0.65</v>
       </c>
       <c r="O2" t="n">
-        <v>34953556190</v>
+        <v>34973490390</v>
       </c>
       <c r="P2" t="n">
         <v>65300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 및 인텔 협력사 선정. 로봇 속도 초가속 등 잭팟 메가톤급 재료 분석.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 및 인텔, AMD와의 파트너십 부각, 로봇 속도 초가속 기술력 기반 주가 급등 전망.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', '인텔']</t>
+          <t>['NPU', '휴머노이드', '기술력']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -670,13 +670,13 @@
         <v>-0.22</v>
       </c>
       <c r="E3" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F3" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3" t="n">
-        <v>293</v>
+        <v>310</v>
       </c>
       <c r="H3" t="n">
         <v>0.48</v>
@@ -702,7 +702,7 @@
         <v>0.7</v>
       </c>
       <c r="O3" t="n">
-        <v>5298409564</v>
+        <v>5360572659</v>
       </c>
       <c r="P3" t="n">
         <v>4760</v>
@@ -762,13 +762,13 @@
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>131563840750</v>
+        <v>134409009550</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>반도체 업황 개선 기대 속에서 주가 상승 모멘텀. 6만원 이상 매도 구간 및 이격 축소, 20일선 안착 여부 관찰.</t>
+          <t>심텍과의 비교를 통한 코리아써키트 상승 기대감 표출, 20일선 안착 및 신고가 돌파 가능성 언급.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['반도체', '이격축소', '20일선']</t>
+          <t>['키맞추기', '20일선 안착', '신고가']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,11 +843,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>115200</v>
+        <v>114400</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+13.05%</t>
+          <t>'+12.27%</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -860,7 +860,7 @@
         <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H5" t="n">
         <v>18.2</v>
@@ -886,7 +886,7 @@
         <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>255961064550</v>
+        <v>259635334800</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32200</v>
+        <v>32050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.42%</t>
+          <t>'+7.91%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="H6" t="n">
         <v>11.3</v>
@@ -978,7 +978,7 @@
         <v>11.92</v>
       </c>
       <c r="O6" t="n">
-        <v>216809384225</v>
+        <v>220321917300</v>
       </c>
       <c r="P6" t="n">
         <v>75900</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 전력 수요 증가로 인한 전력기기 주식 주목. 다만, 700원 저항선 돌파 여부와 외인/기관 매도세 관찰 필요.</t>
+          <t>AI 전력 수요 폭증으로 인한 전력기기 주 주목, 가온전선 신고점 돌파와 비교하며 대한전선 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI 전력수요', '거래량', '외인기관']</t>
+          <t>['AI 전력수요', '전력기기', '상승 기대']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1038,13 +1038,13 @@
         <v>-0.19</v>
       </c>
       <c r="E7" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0.19</v>
       </c>
       <c r="O7" t="n">
-        <v>54619221670</v>
+        <v>56278905430</v>
       </c>
       <c r="P7" t="n">
         <v>13140</v>
@@ -1119,11 +1119,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30450</v>
+        <v>30400</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.55%</t>
+          <t>'+5.37%</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1136,10 +1136,10 @@
         <v>29</v>
       </c>
       <c r="G8" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="H8" t="n">
-        <v>51.76</v>
+        <v>51.77</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>57600187900</v>
+        <v>59388550675</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6620</v>
+        <v>6570</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.91%</t>
+          <t>'+4.12%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="H9" t="n">
         <v>4.86</v>
@@ -1254,7 +1254,7 @@
         <v>4.95</v>
       </c>
       <c r="O9" t="n">
-        <v>47363447495</v>
+        <v>47884116395</v>
       </c>
       <c r="P9" t="n">
         <v>11760</v>
@@ -1299,31 +1299,31 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14080</v>
+        <v>19040</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.99%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>48</v>
+        <v>102</v>
       </c>
       <c r="F10" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="G10" t="n">
-        <v>89</v>
+        <v>441</v>
       </c>
       <c r="H10" t="n">
-        <v>3.34</v>
+        <v>10.47</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,91 +1331,91 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>13540</v>
+        <v>18290</v>
       </c>
       <c r="K10" t="n">
-        <v>13870</v>
+        <v>18830</v>
       </c>
       <c r="L10" t="n">
-        <v>14650</v>
+        <v>19540</v>
       </c>
       <c r="M10" t="n">
-        <v>13740</v>
+        <v>18540</v>
       </c>
       <c r="N10" t="n">
-        <v>3.68</v>
+        <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>81663648575</v>
+        <v>90326255950</v>
       </c>
       <c r="P10" t="n">
-        <v>20300</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>2885</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>18000</v>
+        <v>-76000</v>
       </c>
       <c r="S10" t="n">
-        <v>5000</v>
+        <v>9000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>미국 증시 폭등 및 LNG 기대감 속 공매도 세력과의 싸움 언급, 대미 투자 수혜주로 10월 전고점 돌파 전망.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['공매도', 'LNG 기대', '대미 투자']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18890</v>
+        <v>13960</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.28%</t>
+          <t>'+3.10%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.27</v>
+        <v>-0.34</v>
       </c>
       <c r="E11" t="n">
+        <v>50</v>
+      </c>
+      <c r="F11" t="n">
+        <v>33</v>
+      </c>
+      <c r="G11" t="n">
         <v>98</v>
       </c>
-      <c r="F11" t="n">
-        <v>55</v>
-      </c>
-      <c r="G11" t="n">
-        <v>394</v>
-      </c>
       <c r="H11" t="n">
-        <v>10.47</v>
+        <v>3.34</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,91 +1423,91 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>18290</v>
+        <v>13540</v>
       </c>
       <c r="K11" t="n">
-        <v>18830</v>
+        <v>13870</v>
       </c>
       <c r="L11" t="n">
-        <v>19540</v>
+        <v>14650</v>
       </c>
       <c r="M11" t="n">
-        <v>18540</v>
+        <v>13740</v>
       </c>
       <c r="N11" t="n">
-        <v>10.74</v>
+        <v>3.68</v>
       </c>
       <c r="O11" t="n">
-        <v>83732676775</v>
+        <v>83991172450</v>
       </c>
       <c r="P11" t="n">
-        <v>40350</v>
+        <v>20300</v>
       </c>
       <c r="Q11" t="n">
-        <v>3320</v>
+        <v>2885</v>
       </c>
       <c r="R11" t="n">
-        <v>-76000</v>
+        <v>18000</v>
       </c>
       <c r="S11" t="n">
-        <v>9000</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>공매도 관련 이슈 제기 및 연기금 매수세 유입. LNG, 원전 관련 수주 기대감.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['공매도', '연기금', 'LNG', '원전']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>327500</v>
+        <v>13340</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.83%</t>
+          <t>'+2.93%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>96</v>
+        <v>56</v>
       </c>
       <c r="F12" t="n">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="G12" t="n">
-        <v>246</v>
+        <v>271</v>
       </c>
       <c r="H12" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,91 +1515,91 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>318500</v>
+        <v>12960</v>
       </c>
       <c r="K12" t="n">
-        <v>333000</v>
+        <v>13500</v>
       </c>
       <c r="L12" t="n">
-        <v>349500</v>
+        <v>14190</v>
       </c>
       <c r="M12" t="n">
-        <v>325000</v>
+        <v>13250</v>
       </c>
       <c r="N12" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>99462323000</v>
+        <v>18829476650</v>
       </c>
       <c r="P12" t="n">
-        <v>635000</v>
+        <v>19380</v>
       </c>
       <c r="Q12" t="n">
-        <v>52600</v>
+        <v>3200</v>
       </c>
       <c r="R12" t="n">
-        <v>-8000</v>
+        <v>-41000</v>
       </c>
       <c r="S12" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>나스닥 폭등 및 구리 가격 상승세에 따른 신고가 돌파 기대. 40만원 목표가 제시.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신고가', '구리', '나스닥']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13280</v>
+        <v>1914500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.47%</t>
+          <t>'+2.49%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E13" t="n">
-        <v>54</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>37</v>
+        <v>484</v>
       </c>
       <c r="G13" t="n">
-        <v>238</v>
+        <v>3124</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>50.17</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>1868000</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>1909000</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>1935000</v>
       </c>
       <c r="M13" t="n">
-        <v>13250</v>
+        <v>1904000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>50.23</v>
       </c>
       <c r="O13" t="n">
-        <v>18715899100</v>
+        <v>2267737616500</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>333000</v>
       </c>
       <c r="R13" t="n">
-        <v>-41000</v>
+        <v>82000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>미국 반도체 주식 폭등에 따른 SK하이닉스 강세 출발 및 200만원 돌파 기대감, AI 관련주 동반 상승 전망.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['AI 주', '반도체 폭등', '200만원 돌파']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1913000</v>
+        <v>326000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.41%</t>
+          <t>'+2.35%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>99</v>
       </c>
       <c r="F14" t="n">
-        <v>478</v>
+        <v>67</v>
       </c>
       <c r="G14" t="n">
-        <v>3258</v>
+        <v>245</v>
       </c>
       <c r="H14" t="n">
-        <v>50.17</v>
+        <v>3.22</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1868000</v>
+        <v>318500</v>
       </c>
       <c r="K14" t="n">
-        <v>1909000</v>
+        <v>333000</v>
       </c>
       <c r="L14" t="n">
-        <v>1935000</v>
+        <v>349500</v>
       </c>
       <c r="M14" t="n">
-        <v>1904000</v>
+        <v>325000</v>
       </c>
       <c r="N14" t="n">
-        <v>50.23</v>
+        <v>3.62</v>
       </c>
       <c r="O14" t="n">
-        <v>2199583973000</v>
+        <v>101126224000</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>635000</v>
       </c>
       <c r="Q14" t="n">
-        <v>333000</v>
+        <v>52600</v>
       </c>
       <c r="R14" t="n">
-        <v>82000</v>
+        <v>-8000</v>
       </c>
       <c r="S14" t="n">
-        <v>44000</v>
+        <v>1000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 반도체 주가 폭등에 따른 국내 증시 동반 상승 기대. AI 관련주 강세 및 200만 돌파 전망.</t>
+          <t>신고가 돌파 및 40만원 안착 기대감, 구리 가격 상승 및 외인 지분율 증가에 따른 추가 상승 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '나스닥']</t>
+          <t>['신고가', '구리 가격', '외인 지분율']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
@@ -1763,11 +1763,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>213000</v>
+        <v>212500</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.40%</t>
+          <t>'+2.16%</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1780,7 +1780,7 @@
         <v>33</v>
       </c>
       <c r="G15" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="H15" t="n">
         <v>75.5</v>
@@ -1806,7 +1806,7 @@
         <v>75.44</v>
       </c>
       <c r="O15" t="n">
-        <v>438389026750</v>
+        <v>451488131250</v>
       </c>
       <c r="P15" t="n">
         <v>243500</v>
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G16" t="n">
-        <v>2314</v>
+        <v>2178</v>
       </c>
       <c r="H16" t="n">
         <v>46.56</v>
@@ -1898,7 +1898,7 @@
         <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1754647726500</v>
+        <v>1817045366500</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 낙관론에 따른 주가 상승 기대감. 배당금 기준일(28일)까지 긍정적 흐름 전망.</t>
+          <t>AI 낙관론 및 배당 기대감으로 인한 주가 상승 전망, 30만원 안착 및 56만원 목표가 언급.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI 낙관론', '배당금', '주가전망']</t>
+          <t>['AI 낙관론', '배당 기대', '목표가']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1947,24 +1947,24 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86400</v>
+        <v>86450</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.29%</t>
+          <t>'+1.35%</t>
         </is>
       </c>
       <c r="D17" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>241</v>
+        <v>255</v>
       </c>
       <c r="F17" t="n">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="G17" t="n">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="H17" t="n">
         <v>23.05</v>
@@ -1990,7 +1990,7 @@
         <v>23.12</v>
       </c>
       <c r="O17" t="n">
-        <v>83333387450</v>
+        <v>96244443250</v>
       </c>
       <c r="P17" t="n">
         <v>139200</v>
@@ -2006,16 +2006,16 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>미국 SMR 투자 확정 및 공급 계약 체결 소식. 가스터빈 관련 기대감.</t>
+          <t>SMR 및 가스터빈 사업 관련 공급 계약 체결 및 대미 투자 확정에 따른 주가 상승 기대감 표출.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '공급계약', '가스터빈']</t>
+          <t>['SMR', '가스터빈', '대미 투자']</t>
         </is>
       </c>
       <c r="X17" t="n">
@@ -2039,24 +2039,24 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10600</v>
+        <v>10670</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.47%</t>
+          <t>'+1.14%</t>
         </is>
       </c>
       <c r="D18" t="n">
         <v>1.01</v>
       </c>
       <c r="E18" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="H18" t="n">
         <v>9.609999999999999</v>
@@ -2082,7 +2082,7 @@
         <v>8.6</v>
       </c>
       <c r="O18" t="n">
-        <v>108698910335</v>
+        <v>110516580610</v>
       </c>
       <c r="P18" t="n">
         <v>11640</v>
@@ -2131,24 +2131,24 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17690</v>
+        <v>17710</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.17%</t>
+          <t>'-0.06%</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>-1.68</v>
       </c>
       <c r="E19" t="n">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="F19" t="n">
         <v>87</v>
       </c>
       <c r="G19" t="n">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="H19" t="n">
         <v>6.22</v>
@@ -2174,7 +2174,7 @@
         <v>7.9</v>
       </c>
       <c r="O19" t="n">
-        <v>123761627340</v>
+        <v>126371946290</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2190,7 +2190,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 주가 상승에 따른 2만원 돌파 기대감. 악성 개미 물량 털기 후 급등 가능성 언급.</t>
+          <t>미국 광통신 시장 호황에 따른 대한광통신 상승 기대감, 2만원 목표 및 상한가 가능성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['미국 광통신', '2만원 돌파', '급등']</t>
+          <t>['광통신', '메타발', '상한가']</t>
         </is>
       </c>
       <c r="X19" t="n">
@@ -2234,13 +2234,13 @@
         <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="F20" t="n">
         <v>41</v>
       </c>
       <c r="G20" t="n">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="H20" t="n">
         <v>26.58</v>
@@ -2266,7 +2266,7 @@
         <v>26.57</v>
       </c>
       <c r="O20" t="n">
-        <v>13676793515</v>
+        <v>14019948820</v>
       </c>
       <c r="P20" t="n">
         <v>17950</v>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>회사의 재무 실적 부진 및 장기적인 비전 부재에 대한 부정적 의견. 외국인 매도세 관찰.</t>
+          <t>삼성전자 및 SK하이닉스와의 비교를 통한 LG디스플레이의 낮은 주가 및 부진에 대한 불만 표출.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['적자', '외인매도', '비전']</t>
+          <t>['재무 실적', '적자', '부진']</t>
         </is>
       </c>
       <c r="X20" t="n">
@@ -2329,7 +2329,7 @@
         <v>59</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G21" t="n">
         <v>163</v>
@@ -2358,7 +2358,7 @@
         <v>1.25</v>
       </c>
       <c r="O21" t="n">
-        <v>41584057550</v>
+        <v>42119391025</v>
       </c>
       <c r="P21" t="n">
         <v>22900</v>
@@ -2407,11 +2407,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24300</v>
+        <v>24350</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.76%</t>
+          <t>'-3.56%</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2424,7 +2424,7 @@
         <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="H22" t="n">
         <v>1.76</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>90990762325</v>
+        <v>91656828325</v>
       </c>
       <c r="P22" t="n">
         <v>39350</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3850</v>
+        <v>3840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-5.06%</t>
+          <t>'-5.30%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.63</v>
       </c>
       <c r="E23" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F23" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G23" t="n">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="H23" t="n">
         <v>0.96</v>
@@ -2542,7 +2542,7 @@
         <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>8799102305</v>
+        <v>9020938993</v>
       </c>
       <c r="P23" t="n">
         <v>6480</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10390</v>
+        <v>10430</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.06%</t>
+          <t>'-5.70%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F24" t="n">
         <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="H24" t="n">
         <v>17.89</v>
@@ -2634,7 +2634,7 @@
         <v>18.29</v>
       </c>
       <c r="O24" t="n">
-        <v>32645106375</v>
+        <v>33389493425</v>
       </c>
       <c r="P24" t="n">
         <v>22450</v>

--- a/data/trending_integrated_20260922_11.xlsx
+++ b/data/trending_integrated_20260922_11.xlsx
@@ -563,31 +563,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22550</v>
+        <v>2885</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+29.97%</t>
+          <t>'+29.95%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.04</v>
+        <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>109</v>
+        <v>60</v>
       </c>
       <c r="F2" t="n">
-        <v>79</v>
+        <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>216</v>
+        <v>338</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.48</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -595,47 +595,47 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>17350</v>
+        <v>2220</v>
       </c>
       <c r="K2" t="n">
-        <v>19100</v>
+        <v>2410</v>
       </c>
       <c r="L2" t="n">
-        <v>22550</v>
+        <v>2885</v>
       </c>
       <c r="M2" t="n">
-        <v>18620</v>
+        <v>2410</v>
       </c>
       <c r="N2" t="n">
-        <v>0.65</v>
+        <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>34973490390</v>
+        <v>5365785854</v>
       </c>
       <c r="P2" t="n">
-        <v>65300</v>
+        <v>4760</v>
       </c>
       <c r="Q2" t="n">
-        <v>15130</v>
+        <v>973</v>
       </c>
       <c r="R2" t="n">
-        <v>138000</v>
+        <v>231000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 및 인텔, AMD와의 파트너십 부각, 로봇 속도 초가속 기술력 기반 주가 급등 전망.</t>
+          <t>악재 해소 및 기관 투자자 주목. 휴니버스 글로벌, 항암 백신 관련 긍정적 분석 및 공매도 상환가격 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', '기술력']</t>
+          <t>['항암백신', '공매도', '휴니버스']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -643,91 +643,91 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>486990</t>
+          <t>299660</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2885</v>
+        <v>67300</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+29.95%</t>
+          <t>'+28.68%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.22</v>
+        <v>-0.01</v>
       </c>
       <c r="E3" t="n">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="F3" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>310</v>
+        <v>98</v>
       </c>
       <c r="H3" t="n">
-        <v>0.48</v>
+        <v>6.87</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>2220</v>
+        <v>52300</v>
       </c>
       <c r="K3" t="n">
-        <v>2410</v>
+        <v>60800</v>
       </c>
       <c r="L3" t="n">
-        <v>2885</v>
+        <v>67900</v>
       </c>
       <c r="M3" t="n">
-        <v>2410</v>
+        <v>59700</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7</v>
+        <v>6.88</v>
       </c>
       <c r="O3" t="n">
-        <v>5360572659</v>
+        <v>136001842700</v>
       </c>
       <c r="P3" t="n">
-        <v>4760</v>
+        <v>148300</v>
       </c>
       <c r="Q3" t="n">
-        <v>973</v>
+        <v>16300</v>
       </c>
       <c r="R3" t="n">
-        <v>231000</v>
+        <v>-2000</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>악재 해소 및 기관 투자자 주목. 휴니버스 글로벌, 항암 백신 관련 긍정적 분석 및 공매도 상환가격 언급.</t>
+          <t>상승 흐름 및 신고가 돌파 기대감 언급. 반도체 업종에 대한 장기 투자 회의적인 시각도 존재. 6만원 위에서 매도 의견 제시.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['항암백신', '공매도', '휴니버스']</t>
+          <t>['반도체', '신고가', '추세']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -735,91 +735,91 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>299660</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66800</v>
+        <v>22050</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+27.72%</t>
+          <t>'+27.09%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="G4" t="n">
-        <v>96</v>
+        <v>228</v>
       </c>
       <c r="H4" t="n">
-        <v>6.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>52300</v>
+        <v>17350</v>
       </c>
       <c r="K4" t="n">
-        <v>60800</v>
+        <v>19100</v>
       </c>
       <c r="L4" t="n">
-        <v>67900</v>
+        <v>22550</v>
       </c>
       <c r="M4" t="n">
-        <v>59700</v>
+        <v>18620</v>
       </c>
       <c r="N4" t="n">
-        <v>6.88</v>
+        <v>0.65</v>
       </c>
       <c r="O4" t="n">
-        <v>134409009550</v>
+        <v>45318711890</v>
       </c>
       <c r="P4" t="n">
-        <v>148300</v>
+        <v>65300</v>
       </c>
       <c r="Q4" t="n">
-        <v>16300</v>
+        <v>15130</v>
       </c>
       <c r="R4" t="n">
-        <v>-2000</v>
+        <v>138000</v>
       </c>
       <c r="S4" t="n">
-        <v>49000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>심텍과의 비교를 통한 코리아써키트 상승 기대감 표출, 20일선 안착 및 신고가 돌파 가능성 언급.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스로 인한 기대감. 인텔, AMD, 메타 등 빅테크 기업과의 파트너십 언급. 7배 초가속 등 구체적인 기술력 강조. 2만원 목표.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['키맞추기', '20일선 안착', '신고가']</t>
+          <t>['NPU', '휴머노이드', '빅테크']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>486990</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114400</v>
+        <v>114100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.27%</t>
+          <t>'+11.97%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F5" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="H5" t="n">
         <v>18.2</v>
@@ -886,7 +886,7 @@
         <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>259635334800</v>
+        <v>263315165100</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32050</v>
+        <v>31950</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.91%</t>
+          <t>'+7.58%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G6" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H6" t="n">
         <v>11.3</v>
@@ -978,7 +978,7 @@
         <v>11.92</v>
       </c>
       <c r="O6" t="n">
-        <v>220321917300</v>
+        <v>222217321950</v>
       </c>
       <c r="P6" t="n">
         <v>75900</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 전력 수요 폭증으로 인한 전력기기 주 주목, 가온전선 신고점 돌파와 비교하며 대한전선 상승 기대감 표출.</t>
+          <t>AI 전력수요 폭증 관련주로 언급되었으나, 가온전선과의 비교 등 주가 흐름에 대한 상반된 의견 존재. 단기 목표가 제시. 외인/기관 매도 움직임 포착.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI 전력수요', '전력기기', '상승 기대']</t>
+          <t>['AI 전력수요', '주가 흐름', '외인/기관']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1044,7 +1044,7 @@
         <v>51</v>
       </c>
       <c r="G7" t="n">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -1070,7 +1070,7 @@
         <v>0.19</v>
       </c>
       <c r="O7" t="n">
-        <v>56278905430</v>
+        <v>57535419800</v>
       </c>
       <c r="P7" t="n">
         <v>13140</v>
@@ -1119,27 +1119,27 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30400</v>
+        <v>30500</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.37%</t>
+          <t>'+5.72%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.04</v>
       </c>
       <c r="E8" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F8" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G8" t="n">
         <v>180</v>
       </c>
       <c r="H8" t="n">
-        <v>51.77</v>
+        <v>51.89</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1153,7 +1153,7 @@
         <v>29250</v>
       </c>
       <c r="L8" t="n">
-        <v>30450</v>
+        <v>30500</v>
       </c>
       <c r="M8" t="n">
         <v>29150</v>
@@ -1162,7 +1162,7 @@
         <v>25.79</v>
       </c>
       <c r="O8" t="n">
-        <v>59388550675</v>
+        <v>67912912875</v>
       </c>
       <c r="P8" t="n">
         <v>31200</v>
@@ -1207,215 +1207,215 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6570</v>
+        <v>19040</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.12%</t>
+          <t>'+4.10%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09</v>
+        <v>-0.27</v>
       </c>
       <c r="E9" t="n">
-        <v>50</v>
+        <v>112</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="G9" t="n">
-        <v>134</v>
+        <v>482</v>
       </c>
       <c r="H9" t="n">
-        <v>4.86</v>
+        <v>10.47</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6310</v>
+        <v>18290</v>
       </c>
       <c r="K9" t="n">
-        <v>6460</v>
+        <v>18830</v>
       </c>
       <c r="L9" t="n">
-        <v>7090</v>
+        <v>19540</v>
       </c>
       <c r="M9" t="n">
-        <v>6350</v>
+        <v>18540</v>
       </c>
       <c r="N9" t="n">
-        <v>4.95</v>
+        <v>10.74</v>
       </c>
       <c r="O9" t="n">
-        <v>47884116395</v>
+        <v>98746204875</v>
       </c>
       <c r="P9" t="n">
-        <v>11760</v>
+        <v>40350</v>
       </c>
       <c r="Q9" t="n">
-        <v>1620</v>
+        <v>3320</v>
       </c>
       <c r="R9" t="n">
-        <v>-92000</v>
+        <v>-76000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>미국 증시 폭등 및 원전 관련 뉴스 언급. 공매도 관련 내용 다수 포함. LNG 관련 기대감 존재. 대미원전 프로젝트 수혜주 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['공매도', '원전', 'LNG']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19040</v>
+        <v>6560</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+4.10%</t>
+          <t>'+3.96%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.27</v>
+        <v>-0.09</v>
       </c>
       <c r="E10" t="n">
-        <v>102</v>
+        <v>53</v>
       </c>
       <c r="F10" t="n">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="G10" t="n">
-        <v>441</v>
+        <v>136</v>
       </c>
       <c r="H10" t="n">
-        <v>10.47</v>
+        <v>4.86</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18290</v>
+        <v>6310</v>
       </c>
       <c r="K10" t="n">
-        <v>18830</v>
+        <v>6460</v>
       </c>
       <c r="L10" t="n">
-        <v>19540</v>
+        <v>7090</v>
       </c>
       <c r="M10" t="n">
-        <v>18540</v>
+        <v>6350</v>
       </c>
       <c r="N10" t="n">
-        <v>10.74</v>
+        <v>4.95</v>
       </c>
       <c r="O10" t="n">
-        <v>90326255950</v>
+        <v>48393104635</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>11760</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>1620</v>
       </c>
       <c r="R10" t="n">
-        <v>-76000</v>
+        <v>-92000</v>
       </c>
       <c r="S10" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>미국 증시 폭등 및 LNG 기대감 속 공매도 세력과의 싸움 언급, 대미 투자 수혜주로 10월 전고점 돌파 전망.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', 'LNG 기대', '대미 투자']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13960</v>
+        <v>13390</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.10%</t>
+          <t>'+3.32%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.34</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="F11" t="n">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G11" t="n">
-        <v>98</v>
+        <v>274</v>
       </c>
       <c r="H11" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13540</v>
+        <v>12960</v>
       </c>
       <c r="K11" t="n">
-        <v>13870</v>
+        <v>13500</v>
       </c>
       <c r="L11" t="n">
-        <v>14650</v>
+        <v>14190</v>
       </c>
       <c r="M11" t="n">
-        <v>13740</v>
+        <v>13250</v>
       </c>
       <c r="N11" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>83991172450</v>
+        <v>19087311365</v>
       </c>
       <c r="P11" t="n">
-        <v>20300</v>
+        <v>19380</v>
       </c>
       <c r="Q11" t="n">
-        <v>2885</v>
+        <v>3200</v>
       </c>
       <c r="R11" t="n">
-        <v>18000</v>
+        <v>-41000</v>
       </c>
       <c r="S11" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13340</v>
+        <v>13950</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.93%</t>
+          <t>'+3.03%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F12" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="G12" t="n">
-        <v>271</v>
+        <v>104</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,38 +1515,38 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>12960</v>
+        <v>13540</v>
       </c>
       <c r="K12" t="n">
-        <v>13500</v>
+        <v>13870</v>
       </c>
       <c r="L12" t="n">
-        <v>14190</v>
+        <v>14650</v>
       </c>
       <c r="M12" t="n">
-        <v>13250</v>
+        <v>13740</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>18829476650</v>
+        <v>84729471255</v>
       </c>
       <c r="P12" t="n">
-        <v>19380</v>
+        <v>20300</v>
       </c>
       <c r="Q12" t="n">
-        <v>3200</v>
+        <v>2885</v>
       </c>
       <c r="R12" t="n">
-        <v>-41000</v>
+        <v>18000</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
@@ -1555,11 +1555,11 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,38 +1568,38 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1914500</v>
+        <v>326500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.49%</t>
+          <t>'+2.51%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.06</v>
+        <v>-0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>800</v>
+        <v>103</v>
       </c>
       <c r="F13" t="n">
-        <v>484</v>
+        <v>70</v>
       </c>
       <c r="G13" t="n">
-        <v>3124</v>
+        <v>253</v>
       </c>
       <c r="H13" t="n">
-        <v>50.17</v>
+        <v>3.22</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,51 +1607,51 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>1868000</v>
+        <v>318500</v>
       </c>
       <c r="K13" t="n">
-        <v>1909000</v>
+        <v>333000</v>
       </c>
       <c r="L13" t="n">
-        <v>1935000</v>
+        <v>349500</v>
       </c>
       <c r="M13" t="n">
-        <v>1904000</v>
+        <v>325000</v>
       </c>
       <c r="N13" t="n">
-        <v>50.23</v>
+        <v>3.62</v>
       </c>
       <c r="O13" t="n">
-        <v>2267737616500</v>
+        <v>102509180750</v>
       </c>
       <c r="P13" t="n">
-        <v>2987000</v>
+        <v>635000</v>
       </c>
       <c r="Q13" t="n">
-        <v>333000</v>
+        <v>52600</v>
       </c>
       <c r="R13" t="n">
-        <v>82000</v>
+        <v>-8000</v>
       </c>
       <c r="S13" t="n">
-        <v>44000</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>미국 반도체 주식 폭등에 따른 SK하이닉스 강세 출발 및 200만원 돌파 기대감, AI 관련주 동반 상승 전망.</t>
+          <t>신고가 돌파 및 40만원, 50만원 목표가 제시. 구리 가격 상승 및 모더나 폭등 등 긍정적 재료 언급. 외인 지분율 변화 주시. 단타 주의.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['AI 주', '반도체 폭등', '200만원 돌파']</t>
+          <t>['신고가', '구리 가격', '외인 지분율']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>326000</v>
+        <v>213000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.35%</t>
+          <t>'+2.40%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.4</v>
+        <v>0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="F14" t="n">
-        <v>67</v>
+        <v>34</v>
       </c>
       <c r="G14" t="n">
-        <v>245</v>
+        <v>198</v>
       </c>
       <c r="H14" t="n">
-        <v>3.22</v>
+        <v>75.5</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,47 +1699,47 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>318500</v>
+        <v>208000</v>
       </c>
       <c r="K14" t="n">
-        <v>333000</v>
+        <v>215000</v>
       </c>
       <c r="L14" t="n">
-        <v>349500</v>
+        <v>215000</v>
       </c>
       <c r="M14" t="n">
-        <v>325000</v>
+        <v>211000</v>
       </c>
       <c r="N14" t="n">
-        <v>3.62</v>
+        <v>75.44</v>
       </c>
       <c r="O14" t="n">
-        <v>101126224000</v>
+        <v>462371935000</v>
       </c>
       <c r="P14" t="n">
-        <v>635000</v>
+        <v>243500</v>
       </c>
       <c r="Q14" t="n">
-        <v>52600</v>
+        <v>64700</v>
       </c>
       <c r="R14" t="n">
-        <v>-8000</v>
+        <v>-691000</v>
       </c>
       <c r="S14" t="n">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>신고가 돌파 및 40만원 안착 기대감, 구리 가격 상승 및 외인 지분율 증가에 따른 추가 상승 전망.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['신고가', '구리 가격', '외인 지분율']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X14" t="n">
@@ -1747,43 +1747,43 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>212500</v>
+        <v>1912000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.16%</t>
+          <t>'+2.36%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>45</v>
+        <v>800</v>
       </c>
       <c r="F15" t="n">
-        <v>33</v>
+        <v>485</v>
       </c>
       <c r="G15" t="n">
-        <v>198</v>
+        <v>3061</v>
       </c>
       <c r="H15" t="n">
-        <v>75.5</v>
+        <v>50.17</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>208000</v>
+        <v>1868000</v>
       </c>
       <c r="K15" t="n">
-        <v>215000</v>
+        <v>1909000</v>
       </c>
       <c r="L15" t="n">
-        <v>215000</v>
+        <v>1935000</v>
       </c>
       <c r="M15" t="n">
-        <v>211000</v>
+        <v>1904000</v>
       </c>
       <c r="N15" t="n">
-        <v>75.44</v>
+        <v>50.23</v>
       </c>
       <c r="O15" t="n">
-        <v>451488131250</v>
+        <v>2352979122000</v>
       </c>
       <c r="P15" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q15" t="n">
-        <v>64700</v>
+        <v>333000</v>
       </c>
       <c r="R15" t="n">
-        <v>-691000</v>
+        <v>82000</v>
       </c>
       <c r="S15" t="n">
-        <v>13000</v>
+        <v>44000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>미국 증시 및 반도체 주식 폭등에 따른 강세 전망. AI 관련주 상승 수혜 기대. 200선 돌파 및 230-240 목표가 제시. 선순환 기대감.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['AI', '반도체', '미국 증시']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>279500</v>
+        <v>279750</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.01%</t>
+          <t>'+2.10%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G16" t="n">
-        <v>2178</v>
+        <v>2108</v>
       </c>
       <c r="H16" t="n">
         <v>46.56</v>
@@ -1898,7 +1898,7 @@
         <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1817045366500</v>
+        <v>1884549854250</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 낙관론 및 배당 기대감으로 인한 주가 상승 전망, 30만원 안착 및 56만원 목표가 언급.</t>
+          <t>AI 낙관론 및 배당금 기대감으로 상승 전망. 30만원 안착 기대감 속 외인/기관 매수세 유입. HBM 관련 목표가 56만원 제시.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI 낙관론', '배당 기대', '목표가']</t>
+          <t>['AI 낙관론', '배당금', 'HBM']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,267 +1943,267 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86450</v>
+        <v>10680</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.35%</t>
+          <t>'+1.23%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="E17" t="n">
-        <v>255</v>
+        <v>58</v>
       </c>
       <c r="F17" t="n">
-        <v>157</v>
+        <v>41</v>
       </c>
       <c r="G17" t="n">
-        <v>913</v>
+        <v>147</v>
       </c>
       <c r="H17" t="n">
-        <v>23.05</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85300</v>
+        <v>10550</v>
       </c>
       <c r="K17" t="n">
-        <v>87000</v>
+        <v>10730</v>
       </c>
       <c r="L17" t="n">
-        <v>87000</v>
+        <v>11160</v>
       </c>
       <c r="M17" t="n">
-        <v>85200</v>
+        <v>10300</v>
       </c>
       <c r="N17" t="n">
-        <v>23.12</v>
+        <v>8.6</v>
       </c>
       <c r="O17" t="n">
-        <v>96244443250</v>
+        <v>112049249570</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>11640</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>3735</v>
       </c>
       <c r="R17" t="n">
-        <v>-200000</v>
+        <v>209000</v>
       </c>
       <c r="S17" t="n">
-        <v>-4000</v>
+        <v>-38000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>SMR 및 가스터빈 사업 관련 공급 계약 체결 및 대미 투자 확정에 따른 주가 상승 기대감 표출.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '가스터빈', '대미 투자']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10670</v>
+        <v>86250</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.14%</t>
+          <t>'+1.11%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>278</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="G18" t="n">
-        <v>146</v>
+        <v>977</v>
       </c>
       <c r="H18" t="n">
-        <v>9.609999999999999</v>
+        <v>23.05</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10550</v>
+        <v>85300</v>
       </c>
       <c r="K18" t="n">
-        <v>10730</v>
+        <v>87000</v>
       </c>
       <c r="L18" t="n">
-        <v>11160</v>
+        <v>87000</v>
       </c>
       <c r="M18" t="n">
-        <v>10300</v>
+        <v>85200</v>
       </c>
       <c r="N18" t="n">
-        <v>8.6</v>
+        <v>23.12</v>
       </c>
       <c r="O18" t="n">
-        <v>110516580610</v>
+        <v>105163295800</v>
       </c>
       <c r="P18" t="n">
-        <v>11640</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3735</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>209000</v>
+        <v>-200000</v>
       </c>
       <c r="S18" t="n">
-        <v>-38000</v>
+        <v>-4000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>SMR 및 대미 투자 관련 공급 계약 체결 및 추진 확정 소식 언급. 10만 돌파 기대감. 공매도 관련 부정적 언급 존재. 10억 매수 기록.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['SMR', '대미 투자', '공급 계약']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17710</v>
+        <v>8550</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'-0.06%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-1.68</v>
+        <v>0.01</v>
       </c>
       <c r="E19" t="n">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="F19" t="n">
-        <v>87</v>
+        <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>621</v>
+        <v>295</v>
       </c>
       <c r="H19" t="n">
-        <v>6.22</v>
+        <v>26.58</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>17720</v>
+        <v>8520</v>
       </c>
       <c r="K19" t="n">
-        <v>18230</v>
+        <v>8620</v>
       </c>
       <c r="L19" t="n">
-        <v>18750</v>
+        <v>8650</v>
       </c>
       <c r="M19" t="n">
-        <v>17500</v>
+        <v>8410</v>
       </c>
       <c r="N19" t="n">
-        <v>7.9</v>
+        <v>26.57</v>
       </c>
       <c r="O19" t="n">
-        <v>126371946290</v>
+        <v>14415701320</v>
       </c>
       <c r="P19" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q19" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R19" t="n">
-        <v>-545000</v>
+        <v>-418000</v>
       </c>
       <c r="S19" t="n">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 호황에 따른 대한광통신 상승 기대감, 2만원 목표 및 상한가 가능성 언급.</t>
+          <t>중국 반도체 시장 상황 및 LG디스플레이 재무 상태에 대한 부정적 의견 다수. 10500원 돌파 및 10배 수익 가능성 언급 있으나, 적자 회사 지적. 대차잔고 감소.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['광통신', '메타발', '상한가']</t>
+          <t>['반도체', '재무 상태', '대차잔고']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,130 +2212,130 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8500</v>
+        <v>21550</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'-0.23%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0.01</v>
+        <v>-0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>91</v>
+        <v>61</v>
       </c>
       <c r="F20" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G20" t="n">
-        <v>286</v>
+        <v>168</v>
       </c>
       <c r="H20" t="n">
-        <v>26.58</v>
+        <v>1.2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>8520</v>
+        <v>21500</v>
       </c>
       <c r="K20" t="n">
-        <v>8620</v>
+        <v>21200</v>
       </c>
       <c r="L20" t="n">
-        <v>8650</v>
+        <v>22900</v>
       </c>
       <c r="M20" t="n">
-        <v>8410</v>
+        <v>20850</v>
       </c>
       <c r="N20" t="n">
-        <v>26.57</v>
+        <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>14019948820</v>
+        <v>42812415650</v>
       </c>
       <c r="P20" t="n">
-        <v>17950</v>
+        <v>22900</v>
       </c>
       <c r="Q20" t="n">
-        <v>8120</v>
+        <v>9900</v>
       </c>
       <c r="R20" t="n">
-        <v>-418000</v>
+        <v>47000</v>
       </c>
       <c r="S20" t="n">
-        <v>18000</v>
+        <v>-3000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>삼성전자 및 SK하이닉스와의 비교를 통한 LG디스플레이의 낮은 주가 및 부진에 대한 불만 표출.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['재무 실적', '적자', '부진']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21200</v>
+        <v>17720</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'-1.40%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-0.05</v>
+        <v>-1.68</v>
       </c>
       <c r="E21" t="n">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="F21" t="n">
-        <v>37</v>
+        <v>90</v>
       </c>
       <c r="G21" t="n">
-        <v>163</v>
+        <v>636</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2</v>
+        <v>6.22</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -2343,60 +2343,60 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>21500</v>
+        <v>17720</v>
       </c>
       <c r="K21" t="n">
-        <v>21200</v>
+        <v>18230</v>
       </c>
       <c r="L21" t="n">
-        <v>22900</v>
+        <v>18750</v>
       </c>
       <c r="M21" t="n">
-        <v>20850</v>
+        <v>17500</v>
       </c>
       <c r="N21" t="n">
-        <v>1.25</v>
+        <v>7.9</v>
       </c>
       <c r="O21" t="n">
-        <v>42119391025</v>
+        <v>127861657650</v>
       </c>
       <c r="P21" t="n">
-        <v>22900</v>
+        <v>31500</v>
       </c>
       <c r="Q21" t="n">
-        <v>9900</v>
+        <v>1272</v>
       </c>
       <c r="R21" t="n">
-        <v>47000</v>
+        <v>-545000</v>
       </c>
       <c r="S21" t="n">
-        <v>-3000</v>
+        <v>7000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>미국 광통신 시장 호황에 따른 대한광통신 상승 기대감, 2만원 목표 및 상한가 가능성 언급.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['광통신', '메타발', '상한가']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24350</v>
+        <v>24200</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.56%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1.41</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G22" t="n">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H22" t="n">
         <v>1.76</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>91656828325</v>
+        <v>92147469550</v>
       </c>
       <c r="P22" t="n">
         <v>39350</v>
@@ -2499,24 +2499,24 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3840</v>
+        <v>3845</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-5.30%</t>
+          <t>'-5.18%</t>
         </is>
       </c>
       <c r="D23" t="n">
         <v>0.63</v>
       </c>
       <c r="E23" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F23" t="n">
         <v>46</v>
       </c>
       <c r="G23" t="n">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H23" t="n">
         <v>0.96</v>
@@ -2542,7 +2542,7 @@
         <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>9020938993</v>
+        <v>9167526478</v>
       </c>
       <c r="P23" t="n">
         <v>6480</v>
@@ -2591,11 +2591,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10430</v>
+        <v>10380</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.70%</t>
+          <t>'-6.15%</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2608,7 +2608,7 @@
         <v>52</v>
       </c>
       <c r="G24" t="n">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="H24" t="n">
         <v>17.89</v>
@@ -2634,7 +2634,7 @@
         <v>18.29</v>
       </c>
       <c r="O24" t="n">
-        <v>33389493425</v>
+        <v>33844143155</v>
       </c>
       <c r="P24" t="n">
         <v>22450</v>

--- a/data/trending_integrated_20260922_11.xlsx
+++ b/data/trending_integrated_20260922_11.xlsx
@@ -584,7 +584,7 @@
         <v>39</v>
       </c>
       <c r="G2" t="n">
-        <v>338</v>
+        <v>352</v>
       </c>
       <c r="H2" t="n">
         <v>0.48</v>
@@ -610,7 +610,7 @@
         <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>5365785854</v>
+        <v>5378015369</v>
       </c>
       <c r="P2" t="n">
         <v>4760</v>
@@ -655,79 +655,79 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67300</v>
+        <v>22150</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+28.68%</t>
+          <t>'+27.67%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>-0.01</v>
+        <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="G3" t="n">
-        <v>98</v>
+        <v>256</v>
       </c>
       <c r="H3" t="n">
-        <v>6.87</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>52300</v>
+        <v>17350</v>
       </c>
       <c r="K3" t="n">
-        <v>60800</v>
+        <v>19100</v>
       </c>
       <c r="L3" t="n">
-        <v>67900</v>
+        <v>22550</v>
       </c>
       <c r="M3" t="n">
-        <v>59700</v>
+        <v>18620</v>
       </c>
       <c r="N3" t="n">
-        <v>6.88</v>
+        <v>0.65</v>
       </c>
       <c r="O3" t="n">
-        <v>136001842700</v>
+        <v>48775435915</v>
       </c>
       <c r="P3" t="n">
-        <v>148300</v>
+        <v>65300</v>
       </c>
       <c r="Q3" t="n">
-        <v>16300</v>
+        <v>15130</v>
       </c>
       <c r="R3" t="n">
-        <v>-2000</v>
+        <v>138000</v>
       </c>
       <c r="S3" t="n">
-        <v>49000</v>
+        <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>상승 흐름 및 신고가 돌파 기대감 언급. 반도체 업종에 대한 장기 투자 회의적인 시각도 존재. 6만원 위에서 매도 의견 제시.</t>
+          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스. AI 반도체 파트너십 및 로봇 속도 초가속 효과 기대. 잭팟 메가톤급 재료 언급.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['반도체', '신고가', '추세']</t>
+          <t>['NPU', '휴머노이드', 'AI 반도체']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,86 +740,86 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>007810</t>
+          <t>486990</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22050</v>
+        <v>66000</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+27.09%</t>
+          <t>'+26.20%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="F4" t="n">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>228</v>
+        <v>97</v>
       </c>
       <c r="H4" t="n">
-        <v>0.6899999999999999</v>
+        <v>6.87</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>17350</v>
+        <v>52300</v>
       </c>
       <c r="K4" t="n">
-        <v>19100</v>
+        <v>60800</v>
       </c>
       <c r="L4" t="n">
-        <v>22550</v>
+        <v>67900</v>
       </c>
       <c r="M4" t="n">
-        <v>18620</v>
+        <v>59700</v>
       </c>
       <c r="N4" t="n">
-        <v>0.65</v>
+        <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>45318711890</v>
+        <v>141179299550</v>
       </c>
       <c r="P4" t="n">
-        <v>65300</v>
+        <v>148300</v>
       </c>
       <c r="Q4" t="n">
-        <v>15130</v>
+        <v>16300</v>
       </c>
       <c r="R4" t="n">
-        <v>138000</v>
+        <v>-2000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>49000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>국산 NPU 기반 휴머노이드 개발 착수 뉴스로 인한 기대감. 인텔, AMD, 메타 등 빅테크 기업과의 파트너십 언급. 7배 초가속 등 구체적인 기술력 강조. 2만원 목표.</t>
+          <t>반도체 섹터 내 키 맞추기 기대감. 급등세 기록, 6만원 이상 매도 의견 존재.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['NPU', '휴머노이드', '빅테크']</t>
+          <t>['반도체', '키 맞추기', '급등']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,7 +832,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>486990</t>
+          <t>007810</t>
         </is>
       </c>
     </row>
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114100</v>
+        <v>114800</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+11.97%</t>
+          <t>'+12.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>-0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F5" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G5" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="H5" t="n">
         <v>18.2</v>
@@ -886,7 +886,7 @@
         <v>18.32</v>
       </c>
       <c r="O5" t="n">
-        <v>263315165100</v>
+        <v>266284434550</v>
       </c>
       <c r="P5" t="n">
         <v>198000</v>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31950</v>
+        <v>32350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.58%</t>
+          <t>'+8.92%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.62</v>
       </c>
       <c r="E6" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F6" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G6" t="n">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H6" t="n">
         <v>11.3</v>
@@ -978,7 +978,7 @@
         <v>11.92</v>
       </c>
       <c r="O6" t="n">
-        <v>222217321950</v>
+        <v>225553400825</v>
       </c>
       <c r="P6" t="n">
         <v>75900</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 전력수요 폭증 관련주로 언급되었으나, 가온전선과의 비교 등 주가 흐름에 대한 상반된 의견 존재. 단기 목표가 제시. 외인/기관 매도 움직임 포착.</t>
+          <t>AI 전력 수요 폭증 관련 전력기기 주식 주목. 신고점 돌파 가온전선 대비 저조한 흐름이나, 대량 거래량 동반 상승 분위기 감지.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI 전력수요', '주가 흐름', '외인/기관']</t>
+          <t>['AI 전력 수요', '거래량', '전고점']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6230</v>
+        <v>30550</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+6.31%</t>
+          <t>'+5.89%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.19</v>
+        <v>-0.04</v>
       </c>
       <c r="E7" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="F7" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="G7" t="n">
-        <v>119</v>
+        <v>188</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>51.91</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>5860</v>
+        <v>28850</v>
       </c>
       <c r="K7" t="n">
-        <v>6200</v>
+        <v>29250</v>
       </c>
       <c r="L7" t="n">
-        <v>6610</v>
+        <v>30550</v>
       </c>
       <c r="M7" t="n">
-        <v>6150</v>
+        <v>29150</v>
       </c>
       <c r="N7" t="n">
-        <v>0.19</v>
+        <v>25.79</v>
       </c>
       <c r="O7" t="n">
-        <v>57535419800</v>
+        <v>71175445025</v>
       </c>
       <c r="P7" t="n">
-        <v>13140</v>
+        <v>31200</v>
       </c>
       <c r="Q7" t="n">
-        <v>3725</v>
+        <v>21000</v>
       </c>
       <c r="R7" t="n">
-        <v>48000</v>
+        <v>324000</v>
       </c>
       <c r="S7" t="n">
-        <v>27000</v>
+        <v>118000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 긍정적 전망. 공개매수 및 공매도 세력 관련 언급.</t>
+          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공매도']</t>
+          <t>['국제유가', '환율', '매수세']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30500</v>
+        <v>6200</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.72%</t>
+          <t>'+5.80%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.04</v>
+        <v>-0.19</v>
       </c>
       <c r="E8" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F8" t="n">
-        <v>31</v>
+        <v>51</v>
       </c>
       <c r="G8" t="n">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="H8" t="n">
-        <v>51.89</v>
+        <v>0</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>28850</v>
+        <v>5860</v>
       </c>
       <c r="K8" t="n">
-        <v>29250</v>
+        <v>6200</v>
       </c>
       <c r="L8" t="n">
-        <v>30500</v>
+        <v>6610</v>
       </c>
       <c r="M8" t="n">
-        <v>29150</v>
+        <v>6150</v>
       </c>
       <c r="N8" t="n">
-        <v>25.79</v>
+        <v>0.19</v>
       </c>
       <c r="O8" t="n">
-        <v>67912912875</v>
+        <v>58147342855</v>
       </c>
       <c r="P8" t="n">
-        <v>31200</v>
+        <v>13140</v>
       </c>
       <c r="Q8" t="n">
-        <v>21000</v>
+        <v>3725</v>
       </c>
       <c r="R8" t="n">
-        <v>324000</v>
+        <v>48000</v>
       </c>
       <c r="S8" t="n">
-        <v>118000</v>
+        <v>27000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
+          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 긍정적 전망. 공개매수 및 공매도 세력 관련 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['국제유가', '환율', '매수세']</t>
+          <t>['비트코인', '가상화폐', '공매도']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,202 +1200,202 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19040</v>
+        <v>6560</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+4.10%</t>
+          <t>'+3.96%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.27</v>
+        <v>-0.09</v>
       </c>
       <c r="E9" t="n">
-        <v>112</v>
+        <v>55</v>
       </c>
       <c r="F9" t="n">
-        <v>61</v>
+        <v>35</v>
       </c>
       <c r="G9" t="n">
-        <v>482</v>
+        <v>143</v>
       </c>
       <c r="H9" t="n">
-        <v>10.47</v>
+        <v>4.86</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>18290</v>
+        <v>6310</v>
       </c>
       <c r="K9" t="n">
-        <v>18830</v>
+        <v>6460</v>
       </c>
       <c r="L9" t="n">
-        <v>19540</v>
+        <v>7090</v>
       </c>
       <c r="M9" t="n">
-        <v>18540</v>
+        <v>6350</v>
       </c>
       <c r="N9" t="n">
-        <v>10.74</v>
+        <v>4.95</v>
       </c>
       <c r="O9" t="n">
-        <v>98746204875</v>
+        <v>48560674240</v>
       </c>
       <c r="P9" t="n">
-        <v>40350</v>
+        <v>11760</v>
       </c>
       <c r="Q9" t="n">
-        <v>3320</v>
+        <v>1620</v>
       </c>
       <c r="R9" t="n">
-        <v>-76000</v>
+        <v>-92000</v>
       </c>
       <c r="S9" t="n">
-        <v>9000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미국 증시 폭등 및 원전 관련 뉴스 언급. 공매도 관련 내용 다수 포함. LNG 관련 기대감 존재. 대미원전 프로젝트 수혜주 언급.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['공매도', '원전', 'LNG']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6560</v>
+        <v>18900</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.96%</t>
+          <t>'+3.34%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.09</v>
+        <v>-0.27</v>
       </c>
       <c r="E10" t="n">
-        <v>53</v>
+        <v>114</v>
       </c>
       <c r="F10" t="n">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="G10" t="n">
-        <v>136</v>
+        <v>503</v>
       </c>
       <c r="H10" t="n">
-        <v>4.86</v>
+        <v>10.47</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>6310</v>
+        <v>18290</v>
       </c>
       <c r="K10" t="n">
-        <v>6460</v>
+        <v>18830</v>
       </c>
       <c r="L10" t="n">
-        <v>7090</v>
+        <v>19540</v>
       </c>
       <c r="M10" t="n">
-        <v>6350</v>
+        <v>18540</v>
       </c>
       <c r="N10" t="n">
-        <v>4.95</v>
+        <v>10.74</v>
       </c>
       <c r="O10" t="n">
-        <v>48393104635</v>
+        <v>101445269055</v>
       </c>
       <c r="P10" t="n">
-        <v>11760</v>
+        <v>40350</v>
       </c>
       <c r="Q10" t="n">
-        <v>1620</v>
+        <v>3320</v>
       </c>
       <c r="R10" t="n">
-        <v>-92000</v>
+        <v>-76000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>공매도 구조 및 장부 조작 의혹 제기. 미국 증시 폭등 및 LNG, 원전 사업 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['공매도', 'LNG', '원전']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13390</v>
+        <v>13990</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1403,19 +1403,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="E11" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="F11" t="n">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="G11" t="n">
-        <v>274</v>
+        <v>116</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>12960</v>
+        <v>13540</v>
       </c>
       <c r="K11" t="n">
-        <v>13500</v>
+        <v>13870</v>
       </c>
       <c r="L11" t="n">
-        <v>14190</v>
+        <v>14650</v>
       </c>
       <c r="M11" t="n">
-        <v>13250</v>
+        <v>13740</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="O11" t="n">
-        <v>19087311365</v>
+        <v>85507244895</v>
       </c>
       <c r="P11" t="n">
-        <v>19380</v>
+        <v>20300</v>
       </c>
       <c r="Q11" t="n">
-        <v>3200</v>
+        <v>2885</v>
       </c>
       <c r="R11" t="n">
-        <v>-41000</v>
+        <v>18000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13950</v>
+        <v>328000</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+3.03%</t>
+          <t>'+2.98%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.34</v>
+        <v>-0.4</v>
       </c>
       <c r="E12" t="n">
-        <v>48</v>
+        <v>105</v>
       </c>
       <c r="F12" t="n">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="G12" t="n">
-        <v>104</v>
+        <v>258</v>
       </c>
       <c r="H12" t="n">
-        <v>3.34</v>
+        <v>3.22</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>13540</v>
+        <v>318500</v>
       </c>
       <c r="K12" t="n">
-        <v>13870</v>
+        <v>333000</v>
       </c>
       <c r="L12" t="n">
-        <v>14650</v>
+        <v>349500</v>
       </c>
       <c r="M12" t="n">
-        <v>13740</v>
+        <v>325000</v>
       </c>
       <c r="N12" t="n">
-        <v>3.68</v>
+        <v>3.62</v>
       </c>
       <c r="O12" t="n">
-        <v>84729471255</v>
+        <v>103235915000</v>
       </c>
       <c r="P12" t="n">
-        <v>20300</v>
+        <v>635000</v>
       </c>
       <c r="Q12" t="n">
-        <v>2885</v>
+        <v>52600</v>
       </c>
       <c r="R12" t="n">
-        <v>18000</v>
+        <v>-8000</v>
       </c>
       <c r="S12" t="n">
-        <v>5000</v>
+        <v>1000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>신고가 경신 기대감 및 50만원 목표가 제시. 구리 가격 상승 수혜 가능성 언급. 외인 지분율 변화 주시.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['신고가', '구리 가격', '외인 지분율']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>326500</v>
+        <v>13320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.51%</t>
+          <t>'+2.78%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>103</v>
+        <v>60</v>
       </c>
       <c r="F13" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="G13" t="n">
-        <v>253</v>
+        <v>281</v>
       </c>
       <c r="H13" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>318500</v>
+        <v>12960</v>
       </c>
       <c r="K13" t="n">
-        <v>333000</v>
+        <v>13500</v>
       </c>
       <c r="L13" t="n">
-        <v>349500</v>
+        <v>14190</v>
       </c>
       <c r="M13" t="n">
-        <v>325000</v>
+        <v>13250</v>
       </c>
       <c r="N13" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>102509180750</v>
+        <v>19271751795</v>
       </c>
       <c r="P13" t="n">
-        <v>635000</v>
+        <v>19380</v>
       </c>
       <c r="Q13" t="n">
-        <v>52600</v>
+        <v>3200</v>
       </c>
       <c r="R13" t="n">
-        <v>-8000</v>
+        <v>-41000</v>
       </c>
       <c r="S13" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>신고가 돌파 및 40만원, 50만원 목표가 제시. 구리 가격 상승 및 모더나 폭등 등 긍정적 재료 언급. 외인 지분율 변화 주시. 단타 주의.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['신고가', '구리 가격', '외인 지분율']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>213000</v>
+        <v>1919000</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.40%</t>
+          <t>'+2.73%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.06</v>
+        <v>-0.06</v>
       </c>
       <c r="E14" t="n">
-        <v>46</v>
+        <v>800</v>
       </c>
       <c r="F14" t="n">
-        <v>34</v>
+        <v>481</v>
       </c>
       <c r="G14" t="n">
-        <v>198</v>
+        <v>2834</v>
       </c>
       <c r="H14" t="n">
-        <v>75.5</v>
+        <v>50.17</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,91 +1699,91 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>208000</v>
+        <v>1868000</v>
       </c>
       <c r="K14" t="n">
-        <v>215000</v>
+        <v>1909000</v>
       </c>
       <c r="L14" t="n">
-        <v>215000</v>
+        <v>1935000</v>
       </c>
       <c r="M14" t="n">
-        <v>211000</v>
+        <v>1904000</v>
       </c>
       <c r="N14" t="n">
-        <v>75.44</v>
+        <v>50.23</v>
       </c>
       <c r="O14" t="n">
-        <v>462371935000</v>
+        <v>2418945102500</v>
       </c>
       <c r="P14" t="n">
-        <v>243500</v>
+        <v>2987000</v>
       </c>
       <c r="Q14" t="n">
-        <v>64700</v>
+        <v>333000</v>
       </c>
       <c r="R14" t="n">
-        <v>-691000</v>
+        <v>82000</v>
       </c>
       <c r="S14" t="n">
-        <v>13000</v>
+        <v>44000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>미국 AI 반도체 주가 폭등에 따른 국내 반도체주 강세 기대. 200 이상 상승 전망, 선순환 시작 언급.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['AI 반도체', '미국 증시', '선순환']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>76</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1912000</v>
+        <v>213000</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.36%</t>
+          <t>'+2.40%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.06</v>
+        <v>0.06</v>
       </c>
       <c r="E15" t="n">
-        <v>800</v>
+        <v>48</v>
       </c>
       <c r="F15" t="n">
-        <v>485</v>
+        <v>35</v>
       </c>
       <c r="G15" t="n">
-        <v>3061</v>
+        <v>200</v>
       </c>
       <c r="H15" t="n">
-        <v>50.17</v>
+        <v>75.5</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,60 +1791,60 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>1868000</v>
+        <v>208000</v>
       </c>
       <c r="K15" t="n">
-        <v>1909000</v>
+        <v>215000</v>
       </c>
       <c r="L15" t="n">
-        <v>1935000</v>
+        <v>215000</v>
       </c>
       <c r="M15" t="n">
-        <v>1904000</v>
+        <v>211000</v>
       </c>
       <c r="N15" t="n">
-        <v>50.23</v>
+        <v>75.44</v>
       </c>
       <c r="O15" t="n">
-        <v>2352979122000</v>
+        <v>471908674000</v>
       </c>
       <c r="P15" t="n">
-        <v>2987000</v>
+        <v>243500</v>
       </c>
       <c r="Q15" t="n">
-        <v>333000</v>
+        <v>64700</v>
       </c>
       <c r="R15" t="n">
-        <v>82000</v>
+        <v>-691000</v>
       </c>
       <c r="S15" t="n">
-        <v>44000</v>
+        <v>13000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>미국 증시 및 반도체 주식 폭등에 따른 강세 전망. AI 관련주 상승 수혜 기대. 200선 돌파 및 230-240 목표가 제시. 선순환 기대감.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['AI', '반도체', '미국 증시']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>76</v>
+        <v>2</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1855,11 +1855,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>279750</v>
+        <v>280250</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.10%</t>
+          <t>'+2.28%</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1869,10 +1869,10 @@
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="G16" t="n">
-        <v>2108</v>
+        <v>2101</v>
       </c>
       <c r="H16" t="n">
         <v>46.56</v>
@@ -1898,7 +1898,7 @@
         <v>46.46</v>
       </c>
       <c r="O16" t="n">
-        <v>1884549854250</v>
+        <v>1953379422750</v>
       </c>
       <c r="P16" t="n">
         <v>374500</v>
@@ -1914,16 +1914,16 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 낙관론 및 배당금 기대감으로 상승 전망. 30만원 안착 기대감 속 외인/기관 매수세 유입. HBM 관련 목표가 56만원 제시.</t>
+          <t>AI 낙관론 기반 상승 기대감. 배당금 및 30만 돌파 여부 주목. 외인/기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI 낙관론', '배당금', 'HBM']</t>
+          <t>['AI 낙관론', '배당금', '외인 매수세']</t>
         </is>
       </c>
       <c r="X16" t="n">
@@ -1943,267 +1943,267 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10680</v>
+        <v>86200</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.23%</t>
+          <t>'+1.06%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>58</v>
+        <v>287</v>
       </c>
       <c r="F17" t="n">
-        <v>41</v>
+        <v>167</v>
       </c>
       <c r="G17" t="n">
-        <v>147</v>
+        <v>1031</v>
       </c>
       <c r="H17" t="n">
-        <v>9.609999999999999</v>
+        <v>23.05</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J17" t="n">
-        <v>10550</v>
+        <v>85300</v>
       </c>
       <c r="K17" t="n">
-        <v>10730</v>
+        <v>87000</v>
       </c>
       <c r="L17" t="n">
-        <v>11160</v>
+        <v>87000</v>
       </c>
       <c r="M17" t="n">
-        <v>10300</v>
+        <v>85200</v>
       </c>
       <c r="N17" t="n">
-        <v>8.6</v>
+        <v>23.12</v>
       </c>
       <c r="O17" t="n">
-        <v>112049249570</v>
+        <v>108773033450</v>
       </c>
       <c r="P17" t="n">
-        <v>11640</v>
+        <v>139200</v>
       </c>
       <c r="Q17" t="n">
-        <v>3735</v>
+        <v>57000</v>
       </c>
       <c r="R17" t="n">
-        <v>209000</v>
+        <v>-200000</v>
       </c>
       <c r="S17" t="n">
-        <v>-38000</v>
+        <v>-4000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>SMR, 가스터빈 등 대미 투자 관련 공급 계약 체결 및 추진 확정. 공매도 관련 언급 존재.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['SMR', '대미 투자', '공급 계약']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>86250</v>
+        <v>10620</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+1.11%</t>
+          <t>'+0.66%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="E18" t="n">
-        <v>278</v>
+        <v>59</v>
       </c>
       <c r="F18" t="n">
-        <v>164</v>
+        <v>42</v>
       </c>
       <c r="G18" t="n">
-        <v>977</v>
+        <v>149</v>
       </c>
       <c r="H18" t="n">
-        <v>23.05</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>85300</v>
+        <v>10550</v>
       </c>
       <c r="K18" t="n">
-        <v>87000</v>
+        <v>10730</v>
       </c>
       <c r="L18" t="n">
-        <v>87000</v>
+        <v>11160</v>
       </c>
       <c r="M18" t="n">
-        <v>85200</v>
+        <v>10300</v>
       </c>
       <c r="N18" t="n">
-        <v>23.12</v>
+        <v>8.6</v>
       </c>
       <c r="O18" t="n">
-        <v>105163295800</v>
+        <v>113317885285</v>
       </c>
       <c r="P18" t="n">
-        <v>139200</v>
+        <v>11640</v>
       </c>
       <c r="Q18" t="n">
-        <v>57000</v>
+        <v>3735</v>
       </c>
       <c r="R18" t="n">
-        <v>-200000</v>
+        <v>209000</v>
       </c>
       <c r="S18" t="n">
-        <v>-4000</v>
+        <v>-38000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>SMR 및 대미 투자 관련 공급 계약 체결 및 추진 확정 소식 언급. 10만 돌파 기대감. 공매도 관련 부정적 언급 존재. 10억 매수 기록.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['SMR', '대미 투자', '공급 계약']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>대한광통신</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8550</v>
+        <v>17820</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.56%</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.01</v>
+        <v>-1.68</v>
       </c>
       <c r="E19" t="n">
-        <v>95</v>
+        <v>155</v>
       </c>
       <c r="F19" t="n">
-        <v>41</v>
+        <v>89</v>
       </c>
       <c r="G19" t="n">
-        <v>295</v>
+        <v>639</v>
       </c>
       <c r="H19" t="n">
-        <v>26.58</v>
+        <v>6.22</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J19" t="n">
-        <v>8520</v>
+        <v>17720</v>
       </c>
       <c r="K19" t="n">
-        <v>8620</v>
+        <v>18230</v>
       </c>
       <c r="L19" t="n">
-        <v>8650</v>
+        <v>18750</v>
       </c>
       <c r="M19" t="n">
-        <v>8410</v>
+        <v>17500</v>
       </c>
       <c r="N19" t="n">
-        <v>26.57</v>
+        <v>7.9</v>
       </c>
       <c r="O19" t="n">
-        <v>14415701320</v>
+        <v>129853464040</v>
       </c>
       <c r="P19" t="n">
-        <v>17950</v>
+        <v>31500</v>
       </c>
       <c r="Q19" t="n">
-        <v>8120</v>
+        <v>1272</v>
       </c>
       <c r="R19" t="n">
-        <v>-418000</v>
+        <v>-545000</v>
       </c>
       <c r="S19" t="n">
-        <v>18000</v>
+        <v>7000</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>중국 반도체 시장 상황 및 LG디스플레이 재무 상태에 대한 부정적 의견 다수. 10500원 돌파 및 10배 수익 가능성 언급 있으나, 적자 회사 지적. 대차잔고 감소.</t>
+          <t>미국 광통신 시장 호황에 따른 대한광통신 상승 기대감, 2만원 목표 및 상한가 가능성 언급.</t>
         </is>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>['반도체', '재무 상태', '대차잔고']</t>
+          <t>['광통신', '메타발', '상한가']</t>
         </is>
       </c>
       <c r="X19" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>010170</t>
         </is>
       </c>
     </row>
@@ -2223,24 +2223,24 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21550</v>
+        <v>21600</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.47%</t>
         </is>
       </c>
       <c r="D20" t="n">
         <v>-0.05</v>
       </c>
       <c r="E20" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="F20" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="G20" t="n">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="H20" t="n">
         <v>1.2</v>
@@ -2266,7 +2266,7 @@
         <v>1.25</v>
       </c>
       <c r="O20" t="n">
-        <v>42812415650</v>
+        <v>43367723225</v>
       </c>
       <c r="P20" t="n">
         <v>22900</v>
@@ -2311,83 +2311,83 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17720</v>
+        <v>8550</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.35%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-1.68</v>
+        <v>0.01</v>
       </c>
       <c r="E21" t="n">
-        <v>156</v>
+        <v>97</v>
       </c>
       <c r="F21" t="n">
-        <v>90</v>
+        <v>42</v>
       </c>
       <c r="G21" t="n">
-        <v>636</v>
+        <v>298</v>
       </c>
       <c r="H21" t="n">
-        <v>6.22</v>
+        <v>26.58</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>17720</v>
+        <v>8520</v>
       </c>
       <c r="K21" t="n">
-        <v>18230</v>
+        <v>8620</v>
       </c>
       <c r="L21" t="n">
-        <v>18750</v>
+        <v>8650</v>
       </c>
       <c r="M21" t="n">
-        <v>17500</v>
+        <v>8410</v>
       </c>
       <c r="N21" t="n">
-        <v>7.9</v>
+        <v>26.57</v>
       </c>
       <c r="O21" t="n">
-        <v>127861657650</v>
+        <v>14744438400</v>
       </c>
       <c r="P21" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q21" t="n">
-        <v>1272</v>
+        <v>8120</v>
       </c>
       <c r="R21" t="n">
-        <v>-545000</v>
+        <v>-418000</v>
       </c>
       <c r="S21" t="n">
-        <v>7000</v>
+        <v>18000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>미국 광통신 시장 호황에 따른 대한광통신 상승 기대감, 2만원 목표 및 상한가 가능성 언급.</t>
+          <t>중국 반도체 산업 부진 언급. LGD와 삼성D 비교하며 주가 상승 기대감 약함. 일부 긍정적 재무/기술 기대.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.4</v>
+        <v>0.1</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['광통신', '메타발', '상한가']</t>
+          <t>['중국 반도체', '재무 실적', '기술']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -2407,24 +2407,24 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24200</v>
+        <v>24300</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-3.76%</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>1.41</v>
       </c>
       <c r="E22" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F22" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="G22" t="n">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="H22" t="n">
         <v>1.76</v>
@@ -2450,7 +2450,7 @@
         <v>0.35</v>
       </c>
       <c r="O22" t="n">
-        <v>92147469550</v>
+        <v>93333284050</v>
       </c>
       <c r="P22" t="n">
         <v>39350</v>
@@ -2510,13 +2510,13 @@
         <v>0.63</v>
       </c>
       <c r="E23" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F23" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G23" t="n">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="H23" t="n">
         <v>0.96</v>
@@ -2542,7 +2542,7 @@
         <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>9167526478</v>
+        <v>9270262862</v>
       </c>
       <c r="P23" t="n">
         <v>6480</v>
@@ -2591,24 +2591,24 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10380</v>
+        <v>10430</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-6.15%</t>
+          <t>'-5.70%</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-0.4</v>
       </c>
       <c r="E24" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F24" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G24" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="H24" t="n">
         <v>17.89</v>
@@ -2634,7 +2634,7 @@
         <v>18.29</v>
       </c>
       <c r="O24" t="n">
-        <v>33844143155</v>
+        <v>34164110445</v>
       </c>
       <c r="P24" t="n">
         <v>22450</v>

--- a/data/trending_integrated_20260922_11.xlsx
+++ b/data/trending_integrated_20260922_11.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z24"/>
+  <dimension ref="A1:Z25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>-0.22</v>
       </c>
       <c r="E2" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F2" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="H2" t="n">
         <v>0.48</v>
@@ -610,7 +610,7 @@
         <v>0.7</v>
       </c>
       <c r="O2" t="n">
-        <v>5378015369</v>
+        <v>5383554569</v>
       </c>
       <c r="P2" t="n">
         <v>4760</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22150</v>
+        <v>22250</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+27.67%</t>
+          <t>'+28.24%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.04</v>
       </c>
       <c r="E3" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="F3" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="G3" t="n">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="H3" t="n">
         <v>0.6899999999999999</v>
@@ -702,7 +702,7 @@
         <v>0.65</v>
       </c>
       <c r="O3" t="n">
-        <v>48775435915</v>
+        <v>49961504765</v>
       </c>
       <c r="P3" t="n">
         <v>65300</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>66000</v>
+        <v>66100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+26.20%</t>
+          <t>'+26.39%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>-0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G4" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H4" t="n">
         <v>6.87</v>
@@ -794,7 +794,7 @@
         <v>6.88</v>
       </c>
       <c r="O4" t="n">
-        <v>141179299550</v>
+        <v>144589713850</v>
       </c>
       <c r="P4" t="n">
         <v>148300</v>
@@ -839,79 +839,79 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>삼미금속</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>114800</v>
+        <v>13280</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+12.66%</t>
+          <t>'+19.42%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="F5" t="n">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="G5" t="n">
-        <v>80</v>
+        <v>141</v>
       </c>
       <c r="H5" t="n">
-        <v>18.2</v>
+        <v>0.62</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>101900</v>
+        <v>11120</v>
       </c>
       <c r="K5" t="n">
-        <v>110000</v>
+        <v>11270</v>
       </c>
       <c r="L5" t="n">
-        <v>120700</v>
+        <v>13610</v>
       </c>
       <c r="M5" t="n">
-        <v>109800</v>
+        <v>10810</v>
       </c>
       <c r="N5" t="n">
-        <v>18.32</v>
+        <v>0.7</v>
       </c>
       <c r="O5" t="n">
-        <v>266284434550</v>
+        <v>124817677460</v>
       </c>
       <c r="P5" t="n">
-        <v>198000</v>
+        <v>20850</v>
       </c>
       <c r="Q5" t="n">
-        <v>26350</v>
+        <v>4020</v>
       </c>
       <c r="R5" t="n">
-        <v>234000</v>
+        <v>17000</v>
       </c>
       <c r="S5" t="n">
-        <v>14000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>SK하이닉스 GDDR7 기판 공급망 이슈에 따른 수혜 기대감. 110,000원대 허리 구간에서의 횡보.</t>
+          <t>미국 대규모 투자 1호 텍사스 가스발전 사업 확정 속도. 가스터빈 관련 수혜 기대감 고조. 주가 상승 전망.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['GDDR7', '수혜', '기판']</t>
+          <t>['대미 투자', '가스 발전', '가스터빈']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -919,43 +919,43 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>353200</t>
+          <t>012210</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32350</v>
+        <v>114800</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+8.92%</t>
+          <t>'+12.66%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.62</v>
+        <v>-0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>95</v>
+        <v>59</v>
       </c>
       <c r="F6" t="n">
-        <v>70</v>
+        <v>49</v>
       </c>
       <c r="G6" t="n">
-        <v>171</v>
+        <v>80</v>
       </c>
       <c r="H6" t="n">
-        <v>11.3</v>
+        <v>18.2</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,91 +963,91 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>29700</v>
+        <v>101900</v>
       </c>
       <c r="K6" t="n">
-        <v>30500</v>
+        <v>110000</v>
       </c>
       <c r="L6" t="n">
-        <v>33450</v>
+        <v>120700</v>
       </c>
       <c r="M6" t="n">
-        <v>30000</v>
+        <v>109800</v>
       </c>
       <c r="N6" t="n">
-        <v>11.92</v>
+        <v>18.32</v>
       </c>
       <c r="O6" t="n">
-        <v>225553400825</v>
+        <v>267449060200</v>
       </c>
       <c r="P6" t="n">
-        <v>75900</v>
+        <v>198000</v>
       </c>
       <c r="Q6" t="n">
-        <v>15000</v>
+        <v>26350</v>
       </c>
       <c r="R6" t="n">
-        <v>262000</v>
+        <v>234000</v>
       </c>
       <c r="S6" t="n">
-        <v>4000</v>
+        <v>14000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 전력 수요 폭증 관련 전력기기 주식 주목. 신고점 돌파 가온전선 대비 저조한 흐름이나, 대량 거래량 동반 상승 분위기 감지.</t>
+          <t>SK하이닉스 GDDR7 기판 공급망 이슈에 따른 수혜 기대감. 110,000원대 허리 구간에서의 횡보.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI 전력 수요', '거래량', '전고점']</t>
+          <t>['GDDR7', '수혜', '기판']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>353200</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30550</v>
+        <v>32200</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+5.89%</t>
+          <t>'+8.42%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.04</v>
+        <v>-0.62</v>
       </c>
       <c r="E7" t="n">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="F7" t="n">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="G7" t="n">
-        <v>188</v>
+        <v>176</v>
       </c>
       <c r="H7" t="n">
-        <v>51.91</v>
+        <v>11.3</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,183 +1055,183 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>28850</v>
+        <v>29700</v>
       </c>
       <c r="K7" t="n">
-        <v>29250</v>
+        <v>30500</v>
       </c>
       <c r="L7" t="n">
-        <v>30550</v>
+        <v>33450</v>
       </c>
       <c r="M7" t="n">
-        <v>29150</v>
+        <v>30000</v>
       </c>
       <c r="N7" t="n">
-        <v>25.79</v>
+        <v>11.92</v>
       </c>
       <c r="O7" t="n">
-        <v>71175445025</v>
+        <v>226823119075</v>
       </c>
       <c r="P7" t="n">
-        <v>31200</v>
+        <v>75900</v>
       </c>
       <c r="Q7" t="n">
-        <v>21000</v>
+        <v>15000</v>
       </c>
       <c r="R7" t="n">
-        <v>324000</v>
+        <v>262000</v>
       </c>
       <c r="S7" t="n">
-        <v>118000</v>
+        <v>4000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
+          <t>AI 전력 수요 증가 기대감 속 거래량 증가. 단기 목표가 35,000원 제시. 외인/기관 매도세 관찰.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['국제유가', '환율', '매수세']</t>
+          <t>['AI 전력 수요', '거래량', '목표가']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>001440</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>우리기술투자</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6200</v>
+        <v>280000</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+5.80%</t>
+          <t>'+7.69%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.19</v>
+        <v>0.1</v>
       </c>
       <c r="E8" t="n">
-        <v>67</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>51</v>
+        <v>489</v>
       </c>
       <c r="G8" t="n">
-        <v>116</v>
+        <v>2115</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>46.56</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>5860</v>
+        <v>260000</v>
       </c>
       <c r="K8" t="n">
-        <v>6200</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6610</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6150</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>0.19</v>
+        <v>46.46</v>
       </c>
       <c r="O8" t="n">
-        <v>58147342855</v>
+        <v>2019405000000</v>
       </c>
       <c r="P8" t="n">
-        <v>13140</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3725</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>48000</v>
+        <v>-116000</v>
       </c>
       <c r="S8" t="n">
-        <v>27000</v>
+        <v>128000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 긍정적 전망. 공개매수 및 공매도 세력 관련 언급.</t>
+          <t>AI 낙관론 기반 상승 기대감. 배당금 및 30만 돌파 여부 주목. 외인/기관 매수세 유입.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['비트코인', '가상화폐', '공매도']</t>
+          <t>['AI 낙관론', '배당금', '외인 매수세']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>111</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>041190</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>KBI메탈</t>
+          <t>우리기술투자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6560</v>
+        <v>6240</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'+3.96%</t>
+          <t>'+6.48%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.09</v>
+        <v>-0.19</v>
       </c>
       <c r="E9" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>35</v>
+        <v>52</v>
       </c>
       <c r="G9" t="n">
-        <v>143</v>
+        <v>116</v>
       </c>
       <c r="H9" t="n">
-        <v>4.86</v>
+        <v>0</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,38 +1239,38 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>6310</v>
+        <v>5860</v>
       </c>
       <c r="K9" t="n">
-        <v>6460</v>
+        <v>6200</v>
       </c>
       <c r="L9" t="n">
-        <v>7090</v>
+        <v>6610</v>
       </c>
       <c r="M9" t="n">
-        <v>6350</v>
+        <v>6150</v>
       </c>
       <c r="N9" t="n">
-        <v>4.95</v>
+        <v>0.19</v>
       </c>
       <c r="O9" t="n">
-        <v>48560674240</v>
+        <v>58880127700</v>
       </c>
       <c r="P9" t="n">
-        <v>11760</v>
+        <v>13140</v>
       </c>
       <c r="Q9" t="n">
-        <v>1620</v>
+        <v>3725</v>
       </c>
       <c r="R9" t="n">
-        <v>-92000</v>
+        <v>48000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>27000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
+          <t>비트코인 급등 및 가상화폐 테마 강세에 따른 긍정적 전망. 공개매수 및 공매도 세력 관련 언급.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['기초체력', '외국인매도', '호재뉴스']</t>
+          <t>['비트코인', '가상화폐', '공매도']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>024840</t>
+          <t>041190</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18900</v>
+        <v>30600</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'+3.34%</t>
+          <t>'+6.07%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.27</v>
+        <v>-0.04</v>
       </c>
       <c r="E10" t="n">
-        <v>114</v>
+        <v>50</v>
       </c>
       <c r="F10" t="n">
-        <v>63</v>
+        <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>503</v>
+        <v>193</v>
       </c>
       <c r="H10" t="n">
-        <v>10.47</v>
+        <v>51.92</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,130 +1331,130 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18290</v>
+        <v>28850</v>
       </c>
       <c r="K10" t="n">
-        <v>18830</v>
+        <v>29250</v>
       </c>
       <c r="L10" t="n">
-        <v>19540</v>
+        <v>30600</v>
       </c>
       <c r="M10" t="n">
-        <v>18540</v>
+        <v>29150</v>
       </c>
       <c r="N10" t="n">
-        <v>10.74</v>
+        <v>25.79</v>
       </c>
       <c r="O10" t="n">
-        <v>101445269055</v>
+        <v>73997604025</v>
       </c>
       <c r="P10" t="n">
-        <v>40350</v>
+        <v>31200</v>
       </c>
       <c r="Q10" t="n">
-        <v>3320</v>
+        <v>21000</v>
       </c>
       <c r="R10" t="n">
-        <v>-76000</v>
+        <v>324000</v>
       </c>
       <c r="S10" t="n">
-        <v>9000</v>
+        <v>118000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>공매도 구조 및 장부 조작 의혹 제기. 미국 증시 폭등 및 LNG, 원전 사업 기대감.</t>
+          <t>국제유가 및 환율 하락 속에서 3만원 회복 및 상승 기대감. JP모간 매수세 유입.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['공매도', 'LNG', '원전']</t>
+          <t>['국제유가', '환율', '매수세']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>003490</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대원전선</t>
+          <t>KBI메탈</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13990</v>
+        <v>6590</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'+3.32%</t>
+          <t>'+4.44%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.34</v>
+        <v>-0.09</v>
       </c>
       <c r="E11" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="F11" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G11" t="n">
-        <v>116</v>
+        <v>149</v>
       </c>
       <c r="H11" t="n">
-        <v>3.34</v>
+        <v>4.86</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>13540</v>
+        <v>6310</v>
       </c>
       <c r="K11" t="n">
-        <v>13870</v>
+        <v>6460</v>
       </c>
       <c r="L11" t="n">
-        <v>14650</v>
+        <v>7090</v>
       </c>
       <c r="M11" t="n">
-        <v>13740</v>
+        <v>6350</v>
       </c>
       <c r="N11" t="n">
-        <v>3.68</v>
+        <v>4.95</v>
       </c>
       <c r="O11" t="n">
-        <v>85507244895</v>
+        <v>48719962415</v>
       </c>
       <c r="P11" t="n">
-        <v>20300</v>
+        <v>11760</v>
       </c>
       <c r="Q11" t="n">
-        <v>2885</v>
+        <v>1620</v>
       </c>
       <c r="R11" t="n">
-        <v>18000</v>
+        <v>-92000</v>
       </c>
       <c r="S11" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
+          <t>기초 체력 강화 훈련 및 상승 의지 표명. 외국인 물량 매도에 대한 우려와 호재 뉴스 기대감.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,7 +1463,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['AI 시대', '전력망', '공시']</t>
+          <t>['기초체력', '외국인매도', '호재뉴스']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>006340</t>
+          <t>024840</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>가온전선</t>
+          <t>대원전선</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>328000</v>
+        <v>14005</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'+2.98%</t>
+          <t>'+3.43%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.4</v>
+        <v>-0.34</v>
       </c>
       <c r="E12" t="n">
-        <v>105</v>
+        <v>53</v>
       </c>
       <c r="F12" t="n">
-        <v>71</v>
+        <v>35</v>
       </c>
       <c r="G12" t="n">
-        <v>258</v>
+        <v>117</v>
       </c>
       <c r="H12" t="n">
-        <v>3.22</v>
+        <v>3.34</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,47 +1515,47 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>318500</v>
+        <v>13540</v>
       </c>
       <c r="K12" t="n">
-        <v>333000</v>
+        <v>13870</v>
       </c>
       <c r="L12" t="n">
-        <v>349500</v>
+        <v>14650</v>
       </c>
       <c r="M12" t="n">
-        <v>325000</v>
+        <v>13740</v>
       </c>
       <c r="N12" t="n">
-        <v>3.62</v>
+        <v>3.68</v>
       </c>
       <c r="O12" t="n">
-        <v>103235915000</v>
+        <v>86186799980</v>
       </c>
       <c r="P12" t="n">
-        <v>635000</v>
+        <v>20300</v>
       </c>
       <c r="Q12" t="n">
-        <v>52600</v>
+        <v>2885</v>
       </c>
       <c r="R12" t="n">
-        <v>-8000</v>
+        <v>18000</v>
       </c>
       <c r="S12" t="n">
-        <v>1000</v>
+        <v>5000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>신고가 경신 기대감 및 50만원 목표가 제시. 구리 가격 상승 수혜 가능성 언급. 외인 지분율 변화 주시.</t>
+          <t>AI 시대 전력망 수혜 기대감 속에서 14000원 저항 구간 돌파 시도. 최대주주 변동 공시 확인.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['신고가', '구리 가격', '외인 지분율']</t>
+          <t>['AI 시대', '전력망', '공시']</t>
         </is>
       </c>
       <c r="X12" t="n">
@@ -1563,43 +1563,43 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000500</t>
+          <t>006340</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>가온전선</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13320</v>
+        <v>328500</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'+2.78%</t>
+          <t>'+3.14%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
       <c r="E13" t="n">
-        <v>60</v>
+        <v>108</v>
       </c>
       <c r="F13" t="n">
-        <v>40</v>
+        <v>73</v>
       </c>
       <c r="G13" t="n">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1607,91 +1607,91 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>12960</v>
+        <v>318500</v>
       </c>
       <c r="K13" t="n">
-        <v>13500</v>
+        <v>333000</v>
       </c>
       <c r="L13" t="n">
-        <v>14190</v>
+        <v>349500</v>
       </c>
       <c r="M13" t="n">
-        <v>13250</v>
+        <v>325000</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="O13" t="n">
-        <v>19271751795</v>
+        <v>104173268500</v>
       </c>
       <c r="P13" t="n">
-        <v>19380</v>
+        <v>635000</v>
       </c>
       <c r="Q13" t="n">
-        <v>3200</v>
+        <v>52600</v>
       </c>
       <c r="R13" t="n">
-        <v>-41000</v>
+        <v>-8000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
+          <t>52주 신고가 돌파 및 40만원 목표 제시. 구리 가격 상승 및 모더나 급등 영향. 일부 단타성 매매 관찰.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['플렉트', '공장착공', '매출액']</t>
+          <t>['신고가', '구리 가격', '모더나']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>000500</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1919000</v>
+        <v>18800</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'+2.73%</t>
+          <t>'+2.79%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.06</v>
+        <v>-0.27</v>
       </c>
       <c r="E14" t="n">
-        <v>800</v>
+        <v>121</v>
       </c>
       <c r="F14" t="n">
-        <v>481</v>
+        <v>68</v>
       </c>
       <c r="G14" t="n">
-        <v>2834</v>
+        <v>544</v>
       </c>
       <c r="H14" t="n">
-        <v>50.17</v>
+        <v>10.47</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,51 +1699,51 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>1868000</v>
+        <v>18290</v>
       </c>
       <c r="K14" t="n">
-        <v>1909000</v>
+        <v>18830</v>
       </c>
       <c r="L14" t="n">
-        <v>1935000</v>
+        <v>19540</v>
       </c>
       <c r="M14" t="n">
-        <v>1904000</v>
+        <v>18540</v>
       </c>
       <c r="N14" t="n">
-        <v>50.23</v>
+        <v>10.74</v>
       </c>
       <c r="O14" t="n">
-        <v>2418945102500</v>
+        <v>103608336585</v>
       </c>
       <c r="P14" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q14" t="n">
-        <v>333000</v>
+        <v>3320</v>
       </c>
       <c r="R14" t="n">
-        <v>82000</v>
+        <v>-76000</v>
       </c>
       <c r="S14" t="n">
-        <v>44000</v>
+        <v>9000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>미국 AI 반도체 주가 폭등에 따른 국내 반도체주 강세 기대. 200 이상 상승 전망, 선순환 시작 언급.</t>
+          <t>공매도 관련 의혹 제기 및 감사원 신고 완료. 추석 연휴 LNG 기대감 및 연기금 매수세 유입.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['AI 반도체', '미국 증시', '선순환']</t>
+          <t>['공매도', 'LNG', '연기금']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>76</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,38 +1752,38 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>213000</v>
+        <v>13310</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'+2.40%</t>
+          <t>'+2.70%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F15" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="G15" t="n">
-        <v>200</v>
+        <v>293</v>
       </c>
       <c r="H15" t="n">
-        <v>75.5</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1791,38 +1791,38 @@
         </is>
       </c>
       <c r="J15" t="n">
-        <v>208000</v>
+        <v>12960</v>
       </c>
       <c r="K15" t="n">
-        <v>215000</v>
+        <v>13500</v>
       </c>
       <c r="L15" t="n">
-        <v>215000</v>
+        <v>14190</v>
       </c>
       <c r="M15" t="n">
-        <v>211000</v>
+        <v>13250</v>
       </c>
       <c r="N15" t="n">
-        <v>75.44</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>471908674000</v>
+        <v>19409959085</v>
       </c>
       <c r="P15" t="n">
-        <v>243500</v>
+        <v>19380</v>
       </c>
       <c r="Q15" t="n">
-        <v>64700</v>
+        <v>3200</v>
       </c>
       <c r="R15" t="n">
-        <v>-691000</v>
+        <v>-41000</v>
       </c>
       <c r="S15" t="n">
-        <v>13000</v>
+        <v>0</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
+          <t>광주 삼성전자 플렉트 공장 착공 예정. 정정공시 기반 매출액 증가 확인. 일부 투자자 이탈 및 가격 저항 언급.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,11 +1831,11 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['배당', '자사주 매입', '우선주']</t>
+          <t>['플렉트', '공장착공', '매출액']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>2</v>
+        <v>56</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>280250</v>
+        <v>1918000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'+2.28%</t>
+          <t>'+2.68%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.1</v>
+        <v>-0.06</v>
       </c>
       <c r="E16" t="n">
         <v>800</v>
       </c>
       <c r="F16" t="n">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="G16" t="n">
-        <v>2101</v>
+        <v>2772</v>
       </c>
       <c r="H16" t="n">
-        <v>46.56</v>
+        <v>50.17</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,51 +1883,51 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>274000</v>
+        <v>1868000</v>
       </c>
       <c r="K16" t="n">
-        <v>283000</v>
+        <v>1909000</v>
       </c>
       <c r="L16" t="n">
-        <v>283500</v>
+        <v>1935000</v>
       </c>
       <c r="M16" t="n">
-        <v>278500</v>
+        <v>1904000</v>
       </c>
       <c r="N16" t="n">
-        <v>46.46</v>
+        <v>50.23</v>
       </c>
       <c r="O16" t="n">
-        <v>1953379422750</v>
+        <v>2485254478000</v>
       </c>
       <c r="P16" t="n">
-        <v>374500</v>
+        <v>2987000</v>
       </c>
       <c r="Q16" t="n">
-        <v>81100</v>
+        <v>333000</v>
       </c>
       <c r="R16" t="n">
-        <v>-116000</v>
+        <v>82000</v>
       </c>
       <c r="S16" t="n">
-        <v>128000</v>
+        <v>44000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>AI 낙관론 기반 상승 기대감. 배당금 및 30만 돌파 여부 주목. 외인/기관 매수세 유입.</t>
+          <t>미국 반도체 주가 폭등 및 AI 관련주 강세 영향. SK하이닉스 200만 돌파 및 상승 추세 지속 기대.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['AI 낙관론', '배당금', '외인 매수세']</t>
+          <t>['반도체', 'AI', '상승 추세']</t>
         </is>
       </c>
       <c r="X16" t="n">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
@@ -1936,38 +1936,38 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86200</v>
+        <v>213500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>'+1.06%</t>
+          <t>'+2.64%</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="E17" t="n">
-        <v>287</v>
+        <v>49</v>
       </c>
       <c r="F17" t="n">
-        <v>167</v>
+        <v>36</v>
       </c>
       <c r="G17" t="n">
-        <v>1031</v>
+        <v>202</v>
       </c>
       <c r="H17" t="n">
-        <v>23.05</v>
+        <v>75.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1975,152 +1975,152 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>85300</v>
+        <v>208000</v>
       </c>
       <c r="K17" t="n">
-        <v>87000</v>
+        <v>215000</v>
       </c>
       <c r="L17" t="n">
-        <v>87000</v>
+        <v>215000</v>
       </c>
       <c r="M17" t="n">
-        <v>85200</v>
+        <v>211000</v>
       </c>
       <c r="N17" t="n">
-        <v>23.12</v>
+        <v>75.44</v>
       </c>
       <c r="O17" t="n">
-        <v>108773033450</v>
+        <v>480331064500</v>
       </c>
       <c r="P17" t="n">
-        <v>139200</v>
+        <v>243500</v>
       </c>
       <c r="Q17" t="n">
-        <v>57000</v>
+        <v>64700</v>
       </c>
       <c r="R17" t="n">
-        <v>-200000</v>
+        <v>-691000</v>
       </c>
       <c r="S17" t="n">
-        <v>-4000</v>
+        <v>13000</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>SMR, 가스터빈 등 대미 투자 관련 공급 계약 체결 및 추진 확정. 공매도 관련 언급 존재.</t>
+          <t>배당 기대감 속에 주가 상승 및 21만원 돌파 가능성 언급. 자사주 매입 및 외국인 순매수 시 재진입 고려.</t>
         </is>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>['SMR', '대미 투자', '공급 계약']</t>
+          <t>['배당', '자사주 매입', '우선주']</t>
         </is>
       </c>
       <c r="X17" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>034020</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SFA반도체</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>10620</v>
+        <v>85900</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>'+0.66%</t>
+          <t>'+0.70%</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>59</v>
+        <v>288</v>
       </c>
       <c r="F18" t="n">
-        <v>42</v>
+        <v>166</v>
       </c>
       <c r="G18" t="n">
-        <v>149</v>
+        <v>1059</v>
       </c>
       <c r="H18" t="n">
-        <v>9.609999999999999</v>
+        <v>23.05</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J18" t="n">
-        <v>10550</v>
+        <v>85300</v>
       </c>
       <c r="K18" t="n">
-        <v>10730</v>
+        <v>87000</v>
       </c>
       <c r="L18" t="n">
-        <v>11160</v>
+        <v>87000</v>
       </c>
       <c r="M18" t="n">
-        <v>10300</v>
+        <v>85200</v>
       </c>
       <c r="N18" t="n">
-        <v>8.6</v>
+        <v>23.12</v>
       </c>
       <c r="O18" t="n">
-        <v>113317885285</v>
+        <v>110539092750</v>
       </c>
       <c r="P18" t="n">
-        <v>11640</v>
+        <v>139200</v>
       </c>
       <c r="Q18" t="n">
-        <v>3735</v>
+        <v>57000</v>
       </c>
       <c r="R18" t="n">
-        <v>209000</v>
+        <v>-200000</v>
       </c>
       <c r="S18" t="n">
-        <v>-38000</v>
+        <v>-4000</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
+          <t>대미 투자 SMR 추진 확정 및 공급 계약 체결. 가스터빈 관련 기대감. 일부 투자자들의 매수세 유입.</t>
         </is>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>['외인 매도', '급락', '공매도']</t>
+          <t>['SMR', '공급 계약', '가스터빈']</t>
         </is>
       </c>
       <c r="X18" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>036540</t>
+          <t>034020</t>
         </is>
       </c>
     </row>
@@ -2142,13 +2142,13 @@
         <v>-1.68</v>
       </c>
       <c r="E19" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="F19" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G19" t="n">
-        <v>639</v>
+        <v>648</v>
       </c>
       <c r="H19" t="n">
         <v>6.22</v>
@@ -2174,7 +2174,7 @@
         <v>7.9</v>
       </c>
       <c r="O19" t="n">
-        <v>129853464040</v>
+        <v>131022457195</v>
       </c>
       <c r="P19" t="n">
         <v>31500</v>
@@ -2219,11 +2219,11 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>인제니아테라퓨틱스(Reg.S)</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21600</v>
+        <v>8560</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2231,203 +2231,203 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E20" t="n">
-        <v>66</v>
+        <v>98</v>
       </c>
       <c r="F20" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G20" t="n">
-        <v>183</v>
+        <v>305</v>
       </c>
       <c r="H20" t="n">
-        <v>1.2</v>
+        <v>26.58</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J20" t="n">
-        <v>21500</v>
+        <v>8520</v>
       </c>
       <c r="K20" t="n">
-        <v>21200</v>
+        <v>8620</v>
       </c>
       <c r="L20" t="n">
-        <v>22900</v>
+        <v>8650</v>
       </c>
       <c r="M20" t="n">
-        <v>20850</v>
+        <v>8410</v>
       </c>
       <c r="N20" t="n">
-        <v>1.25</v>
+        <v>26.57</v>
       </c>
       <c r="O20" t="n">
-        <v>43367723225</v>
+        <v>15175821620</v>
       </c>
       <c r="P20" t="n">
-        <v>22900</v>
+        <v>17950</v>
       </c>
       <c r="Q20" t="n">
-        <v>9900</v>
+        <v>8120</v>
       </c>
       <c r="R20" t="n">
-        <v>47000</v>
+        <v>-418000</v>
       </c>
       <c r="S20" t="n">
-        <v>-3000</v>
+        <v>18000</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
+          <t>LG디스플레이의 재무적 실적 평가에 대한 논란. 일부 투자자들의 추가 매수 및 10배 수익 기대.</t>
         </is>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>['임상 3상', '외국인 매수', '머크']</t>
+          <t>['재무 실적', '추가 매수', '수익 기대']</t>
         </is>
       </c>
       <c r="X20" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>950260</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>8550</v>
+        <v>10560</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>'+0.35%</t>
+          <t>'+0.09%</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>0.01</v>
+        <v>1.01</v>
       </c>
       <c r="E21" t="n">
-        <v>97</v>
+        <v>58</v>
       </c>
       <c r="F21" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G21" t="n">
-        <v>298</v>
+        <v>150</v>
       </c>
       <c r="H21" t="n">
-        <v>26.58</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>8520</v>
+        <v>10550</v>
       </c>
       <c r="K21" t="n">
-        <v>8620</v>
+        <v>10730</v>
       </c>
       <c r="L21" t="n">
-        <v>8650</v>
+        <v>11160</v>
       </c>
       <c r="M21" t="n">
-        <v>8410</v>
+        <v>10300</v>
       </c>
       <c r="N21" t="n">
-        <v>26.57</v>
+        <v>8.6</v>
       </c>
       <c r="O21" t="n">
-        <v>14744438400</v>
+        <v>115314924230</v>
       </c>
       <c r="P21" t="n">
-        <v>17950</v>
+        <v>11640</v>
       </c>
       <c r="Q21" t="n">
-        <v>8120</v>
+        <v>3735</v>
       </c>
       <c r="R21" t="n">
-        <v>-418000</v>
+        <v>209000</v>
       </c>
       <c r="S21" t="n">
-        <v>18000</v>
+        <v>-38000</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>중국 반도체 산업 부진 언급. LGD와 삼성D 비교하며 주가 상승 기대감 약함. 일부 긍정적 재무/기술 기대.</t>
+          <t>외인 매도세와 함께 급락하며 '개잡주'라는 비판 제기. 공매도 마지막 발악이라는 분석.</t>
         </is>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>['중국 반도체', '재무 실적', '기술']</t>
+          <t>['외인 매도', '급락', '공매도']</t>
         </is>
       </c>
       <c r="X21" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>036540</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>스카이랩스</t>
+          <t>인제니아테라퓨틱스(Reg.S)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>24300</v>
+        <v>21450</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>'-3.76%</t>
+          <t>'-0.23%</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1.41</v>
+        <v>-0.05</v>
       </c>
       <c r="E22" t="n">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="F22" t="n">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G22" t="n">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="H22" t="n">
-        <v>1.76</v>
+        <v>1.2</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2435,38 +2435,38 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>25250</v>
+        <v>21500</v>
       </c>
       <c r="K22" t="n">
-        <v>26150</v>
+        <v>21200</v>
       </c>
       <c r="L22" t="n">
-        <v>26600</v>
+        <v>22900</v>
       </c>
       <c r="M22" t="n">
-        <v>23800</v>
+        <v>20850</v>
       </c>
       <c r="N22" t="n">
-        <v>0.35</v>
+        <v>1.25</v>
       </c>
       <c r="O22" t="n">
-        <v>93333284050</v>
+        <v>43790495200</v>
       </c>
       <c r="P22" t="n">
-        <v>39350</v>
+        <v>22900</v>
       </c>
       <c r="Q22" t="n">
-        <v>8200</v>
+        <v>9900</v>
       </c>
       <c r="R22" t="n">
-        <v>20000</v>
+        <v>47000</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>-3000</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>삼성과의 협업 기대감 및 코스닥 역사적 종목 성장 전망.</t>
+          <t>머크사의 임상 3상 투자 및 외국인 매수세 유입에 따른 주가 상승 기대.</t>
         </is>
       </c>
       <c r="U22" t="inlineStr"/>
@@ -2475,11 +2475,11 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>['삼성', '협업', '코스닥']</t>
+          <t>['임상 3상', '외국인 매수', '머크']</t>
         </is>
       </c>
       <c r="X22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
@@ -2488,38 +2488,38 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>386380</t>
+          <t>950260</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>미투온</t>
+          <t>스카이랩스</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3845</v>
+        <v>24150</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>'-5.18%</t>
+          <t>'-4.36%</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0.63</v>
+        <v>1.41</v>
       </c>
       <c r="E23" t="n">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="F23" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G23" t="n">
-        <v>261</v>
+        <v>176</v>
       </c>
       <c r="H23" t="n">
-        <v>0.96</v>
+        <v>1.76</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -2527,38 +2527,38 @@
         </is>
       </c>
       <c r="J23" t="n">
-        <v>4055</v>
+        <v>25250</v>
       </c>
       <c r="K23" t="n">
-        <v>4080</v>
+        <v>26150</v>
       </c>
       <c r="L23" t="n">
-        <v>4080</v>
+        <v>26600</v>
       </c>
       <c r="M23" t="n">
-        <v>3825</v>
+        <v>23800</v>
       </c>
       <c r="N23" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="O23" t="n">
-        <v>9270262862</v>
+        <v>93723492275</v>
       </c>
       <c r="P23" t="n">
-        <v>6480</v>
+        <v>39350</v>
       </c>
       <c r="Q23" t="n">
-        <v>1738</v>
+        <v>8200</v>
       </c>
       <c r="R23" t="n">
-        <v>51000</v>
+        <v>20000</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
+          <t>삼성과의 협업 기대감 및 코스닥 역사적 종목 성장 전망.</t>
         </is>
       </c>
       <c r="U23" t="inlineStr"/>
@@ -2567,11 +2567,11 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>['비트코인', '차트분석', '신용물량']</t>
+          <t>['삼성', '협업', '코스닥']</t>
         </is>
       </c>
       <c r="X23" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
@@ -2580,77 +2580,77 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>201490</t>
+          <t>386380</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>광전자</t>
+          <t>미투온</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>10430</v>
+        <v>3835</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>'-5.70%</t>
+          <t>'-5.43%</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>-0.4</v>
+        <v>0.63</v>
       </c>
       <c r="E24" t="n">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F24" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="G24" t="n">
-        <v>196</v>
+        <v>258</v>
       </c>
       <c r="H24" t="n">
-        <v>17.89</v>
+        <v>0.96</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J24" t="n">
-        <v>11060</v>
+        <v>4055</v>
       </c>
       <c r="K24" t="n">
-        <v>10570</v>
+        <v>4080</v>
       </c>
       <c r="L24" t="n">
-        <v>10815</v>
+        <v>4080</v>
       </c>
       <c r="M24" t="n">
-        <v>10060</v>
+        <v>3825</v>
       </c>
       <c r="N24" t="n">
-        <v>18.29</v>
+        <v>0.33</v>
       </c>
       <c r="O24" t="n">
-        <v>34164110445</v>
+        <v>9348129422</v>
       </c>
       <c r="P24" t="n">
-        <v>22450</v>
+        <v>6480</v>
       </c>
       <c r="Q24" t="n">
-        <v>1760</v>
+        <v>1738</v>
       </c>
       <c r="R24" t="n">
-        <v>-11000</v>
+        <v>51000</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>투자경고 종목 지정 속에서 11000원 돌파 기대와 함께 차트 붕괴 및 급락 우려 공존. 종가 양전 시도.</t>
+          <t>비트코인 회복 소식에도 불구하고 미투온 차트상 하락세 지속 및 신용 물량 털어내기 가능성. 인수 및 스테이블 코인 관련 불확실성.</t>
         </is>
       </c>
       <c r="U24" t="inlineStr"/>
@@ -2659,18 +2659,110 @@
       </c>
       <c r="W24" t="inlineStr">
         <is>
+          <t>['비트코인', '차트분석', '신용물량']</t>
+        </is>
+      </c>
+      <c r="X24" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>추적</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>201490</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>광전자</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>10370</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>'-6.24%</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="E25" t="n">
+        <v>74</v>
+      </c>
+      <c r="F25" t="n">
+        <v>54</v>
+      </c>
+      <c r="G25" t="n">
+        <v>200</v>
+      </c>
+      <c r="H25" t="n">
+        <v>17.89</v>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>11060</v>
+      </c>
+      <c r="K25" t="n">
+        <v>10570</v>
+      </c>
+      <c r="L25" t="n">
+        <v>10815</v>
+      </c>
+      <c r="M25" t="n">
+        <v>10060</v>
+      </c>
+      <c r="N25" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="O25" t="n">
+        <v>34513905820</v>
+      </c>
+      <c r="P25" t="n">
+        <v>22450</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>1760</v>
+      </c>
+      <c r="R25" t="n">
+        <v>-11000</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>투자경고 종목 지정 속에서 11000원 돌파 기대와 함께 차트 붕괴 및 급락 우려 공존. 종가 양전 시도.</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
           <t>['투자경고', '돌파', '차트']</t>
         </is>
       </c>
-      <c r="X24" t="n">
+      <c r="X25" t="n">
         <v>7</v>
       </c>
-      <c r="Y24" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>추적</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>017900</t>
         </is>
